--- a/Violence estimates.xlsx
+++ b/Violence estimates.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uob-my.sharepoint.com/personal/vl22683_bristol_ac_uk/Documents/Documents/Misc/UNAIDS/FSW/Analysis/Analysis/Structural-Barriers-FSW-Review/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{AEEE4C1F-92CE-4094-B9C7-1969C8609B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E8F59E3-5D55-4A98-9EFF-642F536CFD28}"/>
+  <xr:revisionPtr revIDLastSave="551" documentId="8_{AEEE4C1F-92CE-4094-B9C7-1969C8609B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FBCDD7D3-F9F4-4C58-806F-EF517414C1F7}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{04E804E8-CF61-42BC-A04D-55E2D33F1781}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{04E804E8-CF61-42BC-A04D-55E2D33F1781}"/>
   </bookViews>
   <sheets>
     <sheet name="All studies" sheetId="12" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="30">
   <si>
     <t>num</t>
   </si>
@@ -132,8 +132,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.000"/>
+  <numFmts count="1">
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
@@ -201,7 +200,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -213,9 +212,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -246,57 +242,6 @@
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="17">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -461,11 +406,62 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <border outline="0">
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -480,36 +476,40 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D9012D00-32F6-4970-A623-C6AEC64A87A7}" name="Table1" displayName="Table1" ref="A1:O60" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1" headerRowBorderDxfId="16" dataCellStyle="Percent">
-  <autoFilter ref="A1:O60" xr:uid="{D9012D00-32F6-4970-A623-C6AEC64A87A7}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O60">
-    <sortCondition ref="A1:A60"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D9012D00-32F6-4970-A623-C6AEC64A87A7}" name="Table1" displayName="Table1" ref="A1:O69" totalsRowShown="0" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" dataCellStyle="Percent">
+  <autoFilter ref="A1:O69" xr:uid="{D9012D00-32F6-4970-A623-C6AEC64A87A7}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O69">
+    <sortCondition ref="A1:A69"/>
   </sortState>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{EA2B369F-CD2A-437E-B2F8-3D03E56D704C}" name="num" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{EA2B369F-CD2A-437E-B2F8-3D03E56D704C}" name="num" dataDxfId="13"/>
     <tableColumn id="2" xr3:uid="{4C6EAEA5-229F-4167-B99B-E76C45A80157}" name="outcome"/>
-    <tableColumn id="3" xr3:uid="{2B35ADD9-C459-4F82-ABBD-5AFBB57A9EF6}" name="violence" dataDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{091F27BE-0323-4291-B253-FDFABBAF668D}" name="name" dataDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{E9C9B534-5035-4C29-A377-B787CF58071B}" name="adjust" dataDxfId="12"/>
-    <tableColumn id="6" xr3:uid="{F66D8C15-4793-439B-A70B-4B553E576366}" name="effect" dataDxfId="11"/>
-    <tableColumn id="7" xr3:uid="{9FC2E3D3-84D0-4F80-9A90-F27EEC63596C}" name="effect_ln" dataDxfId="10" dataCellStyle="Percent">
+    <tableColumn id="3" xr3:uid="{2B35ADD9-C459-4F82-ABBD-5AFBB57A9EF6}" name="violence" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{091F27BE-0323-4291-B253-FDFABBAF668D}" name="name" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{E9C9B534-5035-4C29-A377-B787CF58071B}" name="adjust" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{F66D8C15-4793-439B-A70B-4B553E576366}" name="effect" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{9FC2E3D3-84D0-4F80-9A90-F27EEC63596C}" name="effect_ln" dataDxfId="8" dataCellStyle="Percent">
       <calculatedColumnFormula>LN(F2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{728E5FD9-8A34-4B33-9088-DCD261621DB9}" name="lower" dataDxfId="9"/>
-    <tableColumn id="9" xr3:uid="{64193611-88D8-4061-8512-A8D2A2BD6D2A}" name="lower_ln" dataDxfId="8" dataCellStyle="Percent">
+    <tableColumn id="8" xr3:uid="{728E5FD9-8A34-4B33-9088-DCD261621DB9}" name="lower" dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{64193611-88D8-4061-8512-A8D2A2BD6D2A}" name="lower_ln" dataDxfId="6" dataCellStyle="Percent">
       <calculatedColumnFormula>LN(H2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{28FDE764-6522-406A-B293-D31312FB1464}" name="upper" dataDxfId="7"/>
-    <tableColumn id="11" xr3:uid="{1B360BE7-D329-4CB4-BE36-AE77D8F44371}" name="upper_ln" dataDxfId="6" dataCellStyle="Percent">
+    <tableColumn id="10" xr3:uid="{28FDE764-6522-406A-B293-D31312FB1464}" name="upper" dataDxfId="5"/>
+    <tableColumn id="11" xr3:uid="{1B360BE7-D329-4CB4-BE36-AE77D8F44371}" name="upper_ln" dataDxfId="4" dataCellStyle="Percent">
       <calculatedColumnFormula>LN(J2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{B788DE6B-5B28-440C-96DA-91E1AC36CE91}" name="or_95" dataDxfId="5" dataCellStyle="Percent">
+    <tableColumn id="12" xr3:uid="{B788DE6B-5B28-440C-96DA-91E1AC36CE91}" name="or_95" dataDxfId="3" dataCellStyle="Percent">
       <calculatedColumnFormula>TEXT(F2,"0.00") &amp; " (" &amp; TEXT(H2,"0.00") &amp; "–" &amp; TEXT(J2,"0.00") &amp; ")"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{38118F29-992B-431A-8089-300818351178}" name="i2" dataDxfId="4" dataCellStyle="Percent"/>
-    <tableColumn id="14" xr3:uid="{E626C596-936B-46FD-ADE9-6FBDD07D339D}" name="studies" dataDxfId="3"/>
-    <tableColumn id="15" xr3:uid="{62D2FB13-3C5A-46F5-B258-57D1413A340F}" name="estimates" dataDxfId="2"/>
+    <tableColumn id="13" xr3:uid="{38118F29-992B-431A-8089-300818351178}" name="i2" dataDxfId="2" dataCellStyle="Percent"/>
+    <tableColumn id="14" xr3:uid="{E626C596-936B-46FD-ADE9-6FBDD07D339D}" name="studies" dataDxfId="1"/>
+    <tableColumn id="15" xr3:uid="{62D2FB13-3C5A-46F5-B258-57D1413A340F}" name="estimates" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -832,7 +832,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A692BB3F-BFDA-4F46-BAB1-FC5B2B382277}">
-  <dimension ref="A1:R60"/>
+  <dimension ref="A1:R69"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
@@ -846,50 +846,50 @@
     <col min="15" max="15" width="10.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="J1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="K1" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="L1" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="M1" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="11" t="s">
+      <c r="N1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="O1" s="12" t="s">
+      <c r="O1" s="11" t="s">
         <v>11</v>
       </c>
     </row>
@@ -909,29 +909,41 @@
       <c r="E2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="3"/>
-      <c r="G2" s="8" t="e">
-        <f>LN(F2)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H2" s="3"/>
-      <c r="I2" s="8" t="e">
-        <f>LN(H2)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J2" s="3"/>
-      <c r="K2" s="8" t="e">
-        <f>LN(J2)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L2" s="8" t="str">
-        <f>TEXT(F2,"0.00") &amp; " (" &amp; TEXT(H2,"0.00") &amp; "–" &amp; TEXT(J2,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M2" s="9"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="6"/>
+      <c r="F2" s="3">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="G2" s="7">
+        <f t="shared" ref="G2:G35" si="0">LN(F2)</f>
+        <v>0.13976194237515863</v>
+      </c>
+      <c r="H2" s="3">
+        <v>0.99</v>
+      </c>
+      <c r="I2" s="7">
+        <f t="shared" ref="I2:I35" si="1">LN(H2)</f>
+        <v>-1.0050335853501451E-2</v>
+      </c>
+      <c r="J2" s="3">
+        <v>1.34</v>
+      </c>
+      <c r="K2" s="7">
+        <f t="shared" ref="K2:K35" si="2">LN(J2)</f>
+        <v>0.29266961396282004</v>
+      </c>
+      <c r="L2" s="7" t="str">
+        <f t="shared" ref="L2:L35" si="3">TEXT(F2,"0.00") &amp; " (" &amp; TEXT(H2,"0.00") &amp; "–" &amp; TEXT(J2,"0.00") &amp; ")"</f>
+        <v>1.15 (0.99–1.34)</v>
+      </c>
+      <c r="M2" s="8">
+        <v>0.57799999999999996</v>
+      </c>
+      <c r="N2" s="2">
+        <v>14</v>
+      </c>
+      <c r="O2" s="9">
+        <v>22</v>
+      </c>
+      <c r="P2" s="5"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="4"/>
     </row>
@@ -951,29 +963,41 @@
       <c r="E3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="8" t="e">
-        <f>LN(F3)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="8" t="e">
-        <f>LN(H3)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="8" t="e">
-        <f>LN(J3)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L3" s="8" t="str">
-        <f>TEXT(F3,"0.00") &amp; " (" &amp; TEXT(H3,"0.00") &amp; "–" &amp; TEXT(J3,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M3" s="9"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="10"/>
-      <c r="P3" s="6"/>
+      <c r="F3" s="3">
+        <v>1.64</v>
+      </c>
+      <c r="G3" s="7">
+        <f t="shared" si="0"/>
+        <v>0.494696241836107</v>
+      </c>
+      <c r="H3" s="3">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="I3" s="7">
+        <f t="shared" si="1"/>
+        <v>0.11332868530700327</v>
+      </c>
+      <c r="J3" s="3">
+        <v>2.4</v>
+      </c>
+      <c r="K3" s="7">
+        <f t="shared" si="2"/>
+        <v>0.87546873735389985</v>
+      </c>
+      <c r="L3" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>1.64 (1.12–2.40)</v>
+      </c>
+      <c r="M3" s="8">
+        <v>0.79200000000000004</v>
+      </c>
+      <c r="N3" s="2">
+        <v>5</v>
+      </c>
+      <c r="O3" s="9">
+        <v>5</v>
+      </c>
+      <c r="P3" s="5"/>
       <c r="Q3" s="1"/>
       <c r="R3" s="4"/>
     </row>
@@ -993,29 +1017,41 @@
       <c r="E4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="8" t="e">
-        <f>LN(F4)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H4" s="1"/>
-      <c r="I4" s="8" t="e">
-        <f>LN(H4)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J4" s="1"/>
-      <c r="K4" s="8" t="e">
-        <f>LN(J4)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L4" s="8" t="str">
-        <f>TEXT(F4,"0.00") &amp; " (" &amp; TEXT(H4,"0.00") &amp; "–" &amp; TEXT(J4,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M4" s="9"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="10"/>
-      <c r="P4" s="6"/>
+      <c r="F4" s="3">
+        <v>1.19</v>
+      </c>
+      <c r="G4" s="7">
+        <f t="shared" si="0"/>
+        <v>0.17395330712343798</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0.99</v>
+      </c>
+      <c r="I4" s="7">
+        <f t="shared" si="1"/>
+        <v>-1.0050335853501451E-2</v>
+      </c>
+      <c r="J4" s="1">
+        <v>1.42</v>
+      </c>
+      <c r="K4" s="7">
+        <f t="shared" si="2"/>
+        <v>0.35065687161316933</v>
+      </c>
+      <c r="L4" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>1.19 (0.99–1.42)</v>
+      </c>
+      <c r="M4" s="8">
+        <v>0.63500000000000001</v>
+      </c>
+      <c r="N4" s="1">
+        <v>14</v>
+      </c>
+      <c r="O4" s="9">
+        <v>22</v>
+      </c>
+      <c r="P4" s="5"/>
       <c r="Q4" s="1"/>
       <c r="R4" s="4"/>
     </row>
@@ -1035,29 +1071,41 @@
       <c r="E5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="8" t="e">
+      <c r="F5" s="3">
+        <v>1.62</v>
+      </c>
+      <c r="G5" s="7">
         <f>LN(F5)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="8" t="e">
-        <f>LN(H5)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="8" t="e">
-        <f>LN(J5)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L5" s="8" t="str">
+        <v>0.48242614924429278</v>
+      </c>
+      <c r="H5" s="3">
+        <v>1.27</v>
+      </c>
+      <c r="I5" s="7">
+        <f t="shared" si="1"/>
+        <v>0.23901690047049992</v>
+      </c>
+      <c r="J5" s="3">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="K5" s="7">
+        <f t="shared" si="2"/>
+        <v>0.72754860727727766</v>
+      </c>
+      <c r="L5" s="7" t="str">
         <f>TEXT(F5,"0.00") &amp; " (" &amp; TEXT(H5,"0.00") &amp; "–" &amp; TEXT(J5,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M5" s="9"/>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
-      <c r="P5" s="7"/>
+        <v>1.62 (1.27–2.07)</v>
+      </c>
+      <c r="M5" s="8">
+        <v>0.70599999999999996</v>
+      </c>
+      <c r="N5" s="2">
+        <v>22</v>
+      </c>
+      <c r="O5" s="2">
+        <v>28</v>
+      </c>
+      <c r="P5" s="6"/>
       <c r="Q5" s="2"/>
       <c r="R5" s="4"/>
     </row>
@@ -1077,29 +1125,41 @@
       <c r="E6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="8" t="e">
-        <f>LN(F6)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="8" t="e">
-        <f>LN(H6)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J6" s="3"/>
-      <c r="K6" s="8" t="e">
-        <f>LN(J6)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L6" s="8" t="str">
-        <f>TEXT(F6,"0.00") &amp; " (" &amp; TEXT(H6,"0.00") &amp; "–" &amp; TEXT(J6,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M6" s="9"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="10"/>
-      <c r="P6" s="7"/>
+      <c r="F6" s="3">
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="G6" s="7">
+        <f t="shared" si="0"/>
+        <v>0.88789125735245711</v>
+      </c>
+      <c r="H6" s="3">
+        <v>1.46</v>
+      </c>
+      <c r="I6" s="7">
+        <f t="shared" si="1"/>
+        <v>0.37843643572024505</v>
+      </c>
+      <c r="J6" s="3">
+        <v>4.05</v>
+      </c>
+      <c r="K6" s="7">
+        <f t="shared" si="2"/>
+        <v>1.3987168811184478</v>
+      </c>
+      <c r="L6" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>2.43 (1.46–4.05)</v>
+      </c>
+      <c r="M6" s="8">
+        <v>0.63300000000000001</v>
+      </c>
+      <c r="N6" s="2">
+        <v>7</v>
+      </c>
+      <c r="O6" s="9">
+        <v>9</v>
+      </c>
+      <c r="P6" s="6"/>
       <c r="Q6" s="2"/>
       <c r="R6" s="4"/>
     </row>
@@ -1119,29 +1179,41 @@
       <c r="E7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="8" t="e">
-        <f>LN(F7)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="8" t="e">
-        <f>LN(H7)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J7" s="3"/>
-      <c r="K7" s="8" t="e">
-        <f>LN(J7)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L7" s="8" t="str">
-        <f>TEXT(F7,"0.00") &amp; " (" &amp; TEXT(H7,"0.00") &amp; "–" &amp; TEXT(J7,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M7" s="9"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="10"/>
-      <c r="P7" s="7"/>
+      <c r="F7" s="3">
+        <v>1.55</v>
+      </c>
+      <c r="G7" s="7">
+        <f t="shared" si="0"/>
+        <v>0.43825493093115531</v>
+      </c>
+      <c r="H7" s="3">
+        <v>1.24</v>
+      </c>
+      <c r="I7" s="7">
+        <f t="shared" si="1"/>
+        <v>0.21511137961694549</v>
+      </c>
+      <c r="J7" s="3">
+        <v>1.94</v>
+      </c>
+      <c r="K7" s="7">
+        <f t="shared" si="2"/>
+        <v>0.66268797307523675</v>
+      </c>
+      <c r="L7" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>1.55 (1.24–1.94)</v>
+      </c>
+      <c r="M7" s="8">
+        <v>0.68799999999999994</v>
+      </c>
+      <c r="N7" s="2">
+        <v>22</v>
+      </c>
+      <c r="O7" s="9">
+        <v>28</v>
+      </c>
+      <c r="P7" s="6"/>
       <c r="Q7" s="1"/>
       <c r="R7" s="4"/>
     </row>
@@ -1161,29 +1233,41 @@
       <c r="E8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="8" t="e">
-        <f>LN(F8)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H8" s="3"/>
-      <c r="I8" s="8" t="e">
-        <f>LN(H8)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J8" s="3"/>
-      <c r="K8" s="8" t="e">
-        <f>LN(J8)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L8" s="8" t="str">
-        <f>TEXT(F8,"0.00") &amp; " (" &amp; TEXT(H8,"0.00") &amp; "–" &amp; TEXT(J8,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M8" s="9"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="10"/>
-      <c r="P8" s="7"/>
+      <c r="F8" s="3">
+        <v>1.21</v>
+      </c>
+      <c r="G8" s="7">
+        <f t="shared" si="0"/>
+        <v>0.1906203596086497</v>
+      </c>
+      <c r="H8" s="3">
+        <v>0.96</v>
+      </c>
+      <c r="I8" s="7">
+        <f t="shared" si="1"/>
+        <v>-4.0821994520255166E-2</v>
+      </c>
+      <c r="J8" s="3">
+        <v>1.51</v>
+      </c>
+      <c r="K8" s="7">
+        <f t="shared" si="2"/>
+        <v>0.41210965082683298</v>
+      </c>
+      <c r="L8" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>1.21 (0.96–1.51)</v>
+      </c>
+      <c r="M8" s="8">
+        <v>0.65200000000000002</v>
+      </c>
+      <c r="N8" s="2">
+        <v>13</v>
+      </c>
+      <c r="O8" s="9">
+        <v>18</v>
+      </c>
+      <c r="P8" s="6"/>
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
     </row>
@@ -1203,29 +1287,41 @@
       <c r="E9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="8" t="e">
-        <f>LN(F9)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H9" s="3"/>
-      <c r="I9" s="8" t="e">
-        <f>LN(H9)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J9" s="3"/>
-      <c r="K9" s="8" t="e">
-        <f>LN(J9)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L9" s="8" t="str">
-        <f>TEXT(F9,"0.00") &amp; " (" &amp; TEXT(H9,"0.00") &amp; "–" &amp; TEXT(J9,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M9" s="9"/>
-      <c r="N9" s="2"/>
-      <c r="O9" s="10"/>
-      <c r="P9" s="7"/>
+      <c r="F9" s="3">
+        <v>1.42</v>
+      </c>
+      <c r="G9" s="7">
+        <f t="shared" si="0"/>
+        <v>0.35065687161316933</v>
+      </c>
+      <c r="H9" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="I9" s="7">
+        <f t="shared" si="1"/>
+        <v>9.5310179804324935E-2</v>
+      </c>
+      <c r="J9" s="3">
+        <v>1.83</v>
+      </c>
+      <c r="K9" s="7">
+        <f t="shared" si="2"/>
+        <v>0.60431596685332956</v>
+      </c>
+      <c r="L9" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>1.42 (1.10–1.83)</v>
+      </c>
+      <c r="M9" s="8">
+        <v>0.61199999999999999</v>
+      </c>
+      <c r="N9" s="2">
+        <v>7</v>
+      </c>
+      <c r="O9" s="9">
+        <v>10</v>
+      </c>
+      <c r="P9" s="6"/>
       <c r="Q9" s="2"/>
       <c r="R9" s="4"/>
     </row>
@@ -1245,29 +1341,41 @@
       <c r="E10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="1"/>
-      <c r="G10" s="8" t="e">
-        <f>LN(F10)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H10" s="3"/>
-      <c r="I10" s="8" t="e">
-        <f>LN(H10)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J10" s="1"/>
-      <c r="K10" s="8" t="e">
-        <f>LN(J10)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L10" s="8" t="str">
-        <f>TEXT(F10,"0.00") &amp; " (" &amp; TEXT(H10,"0.00") &amp; "–" &amp; TEXT(J10,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M10" s="9"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="10"/>
-      <c r="P10" s="7"/>
+      <c r="F10" s="1">
+        <v>1.26</v>
+      </c>
+      <c r="G10" s="7">
+        <f t="shared" si="0"/>
+        <v>0.23111172096338664</v>
+      </c>
+      <c r="H10" s="3">
+        <v>1.06</v>
+      </c>
+      <c r="I10" s="7">
+        <f t="shared" si="1"/>
+        <v>5.8268908123975824E-2</v>
+      </c>
+      <c r="J10" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="K10" s="7">
+        <f t="shared" si="2"/>
+        <v>0.40546510810816438</v>
+      </c>
+      <c r="L10" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>1.26 (1.06–1.50)</v>
+      </c>
+      <c r="M10" s="8">
+        <v>0.55600000000000005</v>
+      </c>
+      <c r="N10" s="1">
+        <v>14</v>
+      </c>
+      <c r="O10" s="9">
+        <v>19</v>
+      </c>
+      <c r="P10" s="6"/>
       <c r="Q10" s="2"/>
       <c r="R10" s="4"/>
     </row>
@@ -1287,29 +1395,41 @@
       <c r="E11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F11" s="1"/>
-      <c r="G11" s="8" t="e">
-        <f>LN(F11)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H11" s="3"/>
-      <c r="I11" s="8" t="e">
-        <f>LN(H11)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J11" s="1"/>
-      <c r="K11" s="8" t="e">
-        <f>LN(J11)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L11" s="8" t="str">
-        <f>TEXT(F11,"0.00") &amp; " (" &amp; TEXT(H11,"0.00") &amp; "–" &amp; TEXT(J11,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M11" s="9"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="10"/>
-      <c r="P11" s="7"/>
+      <c r="F11" s="1">
+        <v>1.17</v>
+      </c>
+      <c r="G11" s="7">
+        <f t="shared" si="0"/>
+        <v>0.15700374880966469</v>
+      </c>
+      <c r="H11" s="3">
+        <v>0.78</v>
+      </c>
+      <c r="I11" s="7">
+        <f t="shared" si="1"/>
+        <v>-0.24846135929849961</v>
+      </c>
+      <c r="J11" s="1">
+        <v>1.75</v>
+      </c>
+      <c r="K11" s="7">
+        <f t="shared" si="2"/>
+        <v>0.55961578793542266</v>
+      </c>
+      <c r="L11" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>1.17 (0.78–1.75)</v>
+      </c>
+      <c r="M11" s="8">
+        <v>0.61699999999999999</v>
+      </c>
+      <c r="N11" s="1">
+        <v>5</v>
+      </c>
+      <c r="O11" s="9">
+        <v>6</v>
+      </c>
+      <c r="P11" s="6"/>
       <c r="Q11" s="2"/>
       <c r="R11" s="4"/>
     </row>
@@ -1329,29 +1449,41 @@
       <c r="E12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="1"/>
-      <c r="G12" s="8" t="e">
-        <f>LN(F12)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H12" s="3"/>
-      <c r="I12" s="8" t="e">
-        <f>LN(H12)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J12" s="1"/>
-      <c r="K12" s="8" t="e">
-        <f>LN(J12)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L12" s="8" t="str">
-        <f>TEXT(F12,"0.00") &amp; " (" &amp; TEXT(H12,"0.00") &amp; "–" &amp; TEXT(J12,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M12" s="9"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="10"/>
-      <c r="P12" s="7"/>
+      <c r="F12" s="1">
+        <v>1.36</v>
+      </c>
+      <c r="G12" s="7">
+        <f t="shared" si="0"/>
+        <v>0.30748469974796072</v>
+      </c>
+      <c r="H12" s="3">
+        <v>0.98</v>
+      </c>
+      <c r="I12" s="7">
+        <f t="shared" si="1"/>
+        <v>-2.0202707317519466E-2</v>
+      </c>
+      <c r="J12" s="1">
+        <v>1.87</v>
+      </c>
+      <c r="K12" s="7">
+        <f t="shared" si="2"/>
+        <v>0.62593843086649537</v>
+      </c>
+      <c r="L12" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>1.36 (0.98–1.87)</v>
+      </c>
+      <c r="M12" s="8">
+        <v>0</v>
+      </c>
+      <c r="N12" s="1">
+        <v>3</v>
+      </c>
+      <c r="O12" s="9">
+        <v>4</v>
+      </c>
+      <c r="P12" s="6"/>
       <c r="Q12" s="2"/>
       <c r="R12" s="4"/>
     </row>
@@ -1371,29 +1503,41 @@
       <c r="E13" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F13" s="1"/>
-      <c r="G13" s="8" t="e">
-        <f>LN(F13)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H13" s="3"/>
-      <c r="I13" s="8" t="e">
-        <f>LN(H13)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J13" s="1"/>
-      <c r="K13" s="8" t="e">
-        <f>LN(J13)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L13" s="8" t="str">
-        <f>TEXT(F13,"0.00") &amp; " (" &amp; TEXT(H13,"0.00") &amp; "–" &amp; TEXT(J13,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M13" s="9"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="10"/>
-      <c r="P13" s="7"/>
+      <c r="F13" s="1">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="G13" s="7">
+        <f t="shared" si="0"/>
+        <v>0.13976194237515863</v>
+      </c>
+      <c r="H13" s="3">
+        <v>0.77</v>
+      </c>
+      <c r="I13" s="7">
+        <f t="shared" si="1"/>
+        <v>-0.26136476413440751</v>
+      </c>
+      <c r="J13" s="1">
+        <v>1.71</v>
+      </c>
+      <c r="K13" s="7">
+        <f t="shared" si="2"/>
+        <v>0.53649337051456847</v>
+      </c>
+      <c r="L13" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>1.15 (0.77–1.71)</v>
+      </c>
+      <c r="M13" s="8">
+        <v>0.59099999999999997</v>
+      </c>
+      <c r="N13" s="1">
+        <v>5</v>
+      </c>
+      <c r="O13" s="9">
+        <v>6</v>
+      </c>
+      <c r="P13" s="6"/>
       <c r="Q13" s="1"/>
       <c r="R13" s="4"/>
     </row>
@@ -1413,29 +1557,41 @@
       <c r="E14" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F14" s="1"/>
-      <c r="G14" s="8" t="e">
-        <f>LN(F14)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H14" s="3"/>
-      <c r="I14" s="8" t="e">
-        <f>LN(H14)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J14" s="1"/>
-      <c r="K14" s="8" t="e">
-        <f>LN(J14)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L14" s="8" t="str">
-        <f>TEXT(F14,"0.00") &amp; " (" &amp; TEXT(H14,"0.00") &amp; "–" &amp; TEXT(J14,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M14" s="9"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="10"/>
-      <c r="P14" s="7"/>
+      <c r="F14" s="1">
+        <v>1.32</v>
+      </c>
+      <c r="G14" s="7">
+        <f t="shared" si="0"/>
+        <v>0.27763173659827955</v>
+      </c>
+      <c r="H14" s="3">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="I14" s="7">
+        <f t="shared" si="1"/>
+        <v>0.14842000511827322</v>
+      </c>
+      <c r="J14" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="K14" s="7">
+        <f t="shared" si="2"/>
+        <v>0.40546510810816438</v>
+      </c>
+      <c r="L14" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>1.32 (1.16–1.50)</v>
+      </c>
+      <c r="M14" s="8">
+        <v>0.65200000000000002</v>
+      </c>
+      <c r="N14" s="1">
+        <v>40</v>
+      </c>
+      <c r="O14" s="9">
+        <v>74</v>
+      </c>
+      <c r="P14" s="6"/>
       <c r="Q14" s="1"/>
       <c r="R14" s="4"/>
     </row>
@@ -1455,29 +1611,41 @@
       <c r="E15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="8" t="e">
-        <f>LN(F15)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H15" s="3"/>
-      <c r="I15" s="8" t="e">
-        <f>LN(H15)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J15" s="1"/>
-      <c r="K15" s="8" t="e">
-        <f>LN(J15)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L15" s="8" t="str">
-        <f>TEXT(F15,"0.00") &amp; " (" &amp; TEXT(H15,"0.00") &amp; "–" &amp; TEXT(J15,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M15" s="9"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="10"/>
-      <c r="P15" s="7"/>
+      <c r="F15" s="3">
+        <v>1.6</v>
+      </c>
+      <c r="G15" s="7">
+        <f t="shared" si="0"/>
+        <v>0.47000362924573563</v>
+      </c>
+      <c r="H15" s="3">
+        <v>1.33</v>
+      </c>
+      <c r="I15" s="7">
+        <f t="shared" si="1"/>
+        <v>0.28517894223366247</v>
+      </c>
+      <c r="J15" s="1">
+        <v>1.92</v>
+      </c>
+      <c r="K15" s="7">
+        <f t="shared" si="2"/>
+        <v>0.65232518603969014</v>
+      </c>
+      <c r="L15" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>1.60 (1.33–1.92)</v>
+      </c>
+      <c r="M15" s="8">
+        <v>0.68400000000000005</v>
+      </c>
+      <c r="N15" s="1">
+        <v>19</v>
+      </c>
+      <c r="O15" s="9">
+        <v>28</v>
+      </c>
+      <c r="P15" s="6"/>
       <c r="Q15" s="1"/>
       <c r="R15" s="4"/>
     </row>
@@ -1497,29 +1665,41 @@
       <c r="E16" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="8" t="e">
-        <f>LN(F16)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H16" s="3"/>
-      <c r="I16" s="8" t="e">
-        <f>LN(H16)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J16" s="3"/>
-      <c r="K16" s="8" t="e">
-        <f>LN(J16)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L16" s="8" t="str">
-        <f>TEXT(F16,"0.00") &amp; " (" &amp; TEXT(H16,"0.00") &amp; "–" &amp; TEXT(J16,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M16" s="9"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="10"/>
-      <c r="P16" s="7"/>
+      <c r="F16" s="3">
+        <v>1.31</v>
+      </c>
+      <c r="G16" s="7">
+        <f t="shared" si="0"/>
+        <v>0.27002713721306021</v>
+      </c>
+      <c r="H16" s="3">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="I16" s="7">
+        <f t="shared" si="1"/>
+        <v>0.14842000511827322</v>
+      </c>
+      <c r="J16" s="3">
+        <v>1.48</v>
+      </c>
+      <c r="K16" s="7">
+        <f t="shared" si="2"/>
+        <v>0.39204208777602367</v>
+      </c>
+      <c r="L16" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>1.31 (1.16–1.48)</v>
+      </c>
+      <c r="M16" s="8">
+        <v>0.63400000000000001</v>
+      </c>
+      <c r="N16" s="1">
+        <v>41</v>
+      </c>
+      <c r="O16" s="9">
+        <v>75</v>
+      </c>
+      <c r="P16" s="6"/>
       <c r="Q16" s="1"/>
       <c r="R16" s="4"/>
     </row>
@@ -1539,28 +1719,40 @@
       <c r="E17" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F17" s="3"/>
-      <c r="G17" s="8" t="e">
-        <f>LN(F17)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H17" s="3"/>
-      <c r="I17" s="8" t="e">
-        <f>LN(H17)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J17" s="3"/>
-      <c r="K17" s="8" t="e">
-        <f>LN(J17)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L17" s="8" t="str">
-        <f>TEXT(F17,"0.00") &amp; " (" &amp; TEXT(H17,"0.00") &amp; "–" &amp; TEXT(J17,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M17" s="9"/>
-      <c r="N17" s="2"/>
-      <c r="O17" s="10"/>
+      <c r="F17" s="3">
+        <v>1.42</v>
+      </c>
+      <c r="G17" s="7">
+        <f t="shared" si="0"/>
+        <v>0.35065687161316933</v>
+      </c>
+      <c r="H17" s="3">
+        <v>1.19</v>
+      </c>
+      <c r="I17" s="7">
+        <f t="shared" si="1"/>
+        <v>0.17395330712343798</v>
+      </c>
+      <c r="J17" s="3">
+        <v>1.7</v>
+      </c>
+      <c r="K17" s="7">
+        <f t="shared" si="2"/>
+        <v>0.53062825106217038</v>
+      </c>
+      <c r="L17" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>1.42 (1.19–1.70)</v>
+      </c>
+      <c r="M17" s="8">
+        <v>0.32900000000000001</v>
+      </c>
+      <c r="N17" s="2">
+        <v>14</v>
+      </c>
+      <c r="O17" s="9">
+        <v>21</v>
+      </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
@@ -1578,28 +1770,40 @@
       <c r="E18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="8" t="e">
-        <f>LN(F18)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H18" s="3"/>
-      <c r="I18" s="8" t="e">
-        <f>LN(H18)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J18" s="3"/>
-      <c r="K18" s="8" t="e">
-        <f>LN(J18)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L18" s="8" t="str">
-        <f>TEXT(F18,"0.00") &amp; " (" &amp; TEXT(H18,"0.00") &amp; "–" &amp; TEXT(J18,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M18" s="9"/>
-      <c r="N18" s="2"/>
-      <c r="O18" s="10"/>
+      <c r="F18" s="3">
+        <v>1.32</v>
+      </c>
+      <c r="G18" s="7">
+        <f t="shared" si="0"/>
+        <v>0.27763173659827955</v>
+      </c>
+      <c r="H18" s="3">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="I18" s="7">
+        <f t="shared" si="1"/>
+        <v>0.13976194237515863</v>
+      </c>
+      <c r="J18" s="3">
+        <v>1.52</v>
+      </c>
+      <c r="K18" s="7">
+        <f t="shared" si="2"/>
+        <v>0.41871033485818504</v>
+      </c>
+      <c r="L18" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>1.32 (1.15–1.52)</v>
+      </c>
+      <c r="M18" s="8">
+        <v>0.36099999999999999</v>
+      </c>
+      <c r="N18" s="2">
+        <v>6</v>
+      </c>
+      <c r="O18" s="9">
+        <v>7</v>
+      </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
@@ -1617,28 +1821,40 @@
       <c r="E19" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="8" t="e">
-        <f>LN(F19)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H19" s="1"/>
-      <c r="I19" s="8" t="e">
-        <f>LN(H19)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J19" s="1"/>
-      <c r="K19" s="8" t="e">
-        <f>LN(J19)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L19" s="8" t="str">
-        <f>TEXT(F19,"0.00") &amp; " (" &amp; TEXT(H19,"0.00") &amp; "–" &amp; TEXT(J19,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M19" s="9"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="10"/>
+      <c r="F19" s="3">
+        <v>1.29</v>
+      </c>
+      <c r="G19" s="7">
+        <f t="shared" si="0"/>
+        <v>0.25464221837358075</v>
+      </c>
+      <c r="H19" s="1">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="I19" s="7">
+        <f t="shared" si="1"/>
+        <v>0.13976194237515863</v>
+      </c>
+      <c r="J19" s="1">
+        <v>1.44</v>
+      </c>
+      <c r="K19" s="7">
+        <f t="shared" si="2"/>
+        <v>0.36464311358790924</v>
+      </c>
+      <c r="L19" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>1.29 (1.15–1.44)</v>
+      </c>
+      <c r="M19" s="8">
+        <v>0</v>
+      </c>
+      <c r="N19" s="1">
+        <v>14</v>
+      </c>
+      <c r="O19" s="9">
+        <v>21</v>
+      </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
@@ -1656,28 +1872,40 @@
       <c r="E20" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="8" t="e">
+      <c r="F20" s="3">
+        <v>1.49</v>
+      </c>
+      <c r="G20" s="7">
         <f>LN(F20)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H20" s="3"/>
-      <c r="I20" s="8" t="e">
-        <f>LN(H20)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J20" s="3"/>
-      <c r="K20" s="8" t="e">
-        <f>LN(J20)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L20" s="8" t="str">
+        <v>0.39877611995736778</v>
+      </c>
+      <c r="H20" s="3">
+        <v>1.23</v>
+      </c>
+      <c r="I20" s="7">
+        <f t="shared" si="1"/>
+        <v>0.20701416938432612</v>
+      </c>
+      <c r="J20" s="3">
+        <v>1.8</v>
+      </c>
+      <c r="K20" s="7">
+        <f t="shared" si="2"/>
+        <v>0.58778666490211906</v>
+      </c>
+      <c r="L20" s="7" t="str">
         <f>TEXT(F20,"0.00") &amp; " (" &amp; TEXT(H20,"0.00") &amp; "–" &amp; TEXT(J20,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M20" s="9"/>
-      <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
+        <v>1.49 (1.23–1.80)</v>
+      </c>
+      <c r="M20" s="8">
+        <v>0.78900000000000003</v>
+      </c>
+      <c r="N20" s="1">
+        <v>24</v>
+      </c>
+      <c r="O20" s="1">
+        <v>28</v>
+      </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
@@ -1695,28 +1923,40 @@
       <c r="E21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="8" t="e">
-        <f>LN(F21)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H21" s="3"/>
-      <c r="I21" s="8" t="e">
-        <f>LN(H21)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J21" s="3"/>
-      <c r="K21" s="8" t="e">
-        <f>LN(J21)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L21" s="8" t="str">
-        <f>TEXT(F21,"0.00") &amp; " (" &amp; TEXT(H21,"0.00") &amp; "–" &amp; TEXT(J21,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M21" s="9"/>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
+      <c r="F21" s="3">
+        <v>1.57</v>
+      </c>
+      <c r="G21" s="7">
+        <f t="shared" si="0"/>
+        <v>0.45107561936021673</v>
+      </c>
+      <c r="H21" s="3">
+        <v>1.27</v>
+      </c>
+      <c r="I21" s="7">
+        <f t="shared" si="1"/>
+        <v>0.23901690047049992</v>
+      </c>
+      <c r="J21" s="3">
+        <v>1.93</v>
+      </c>
+      <c r="K21" s="7">
+        <f t="shared" si="2"/>
+        <v>0.65752000291679413</v>
+      </c>
+      <c r="L21" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>1.57 (1.27–1.93)</v>
+      </c>
+      <c r="M21" s="8">
+        <v>0.40200000000000002</v>
+      </c>
+      <c r="N21" s="2">
+        <v>12</v>
+      </c>
+      <c r="O21" s="2">
+        <v>14</v>
+      </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
@@ -1734,28 +1974,40 @@
       <c r="E22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="8" t="e">
-        <f>LN(F22)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H22" s="3"/>
-      <c r="I22" s="8" t="e">
-        <f>LN(H22)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J22" s="3"/>
-      <c r="K22" s="8" t="e">
-        <f>LN(J22)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L22" s="8" t="str">
-        <f>TEXT(F22,"0.00") &amp; " (" &amp; TEXT(H22,"0.00") &amp; "–" &amp; TEXT(J22,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M22" s="9"/>
-      <c r="N22" s="2"/>
-      <c r="O22" s="10"/>
+      <c r="F22" s="3">
+        <v>1.4</v>
+      </c>
+      <c r="G22" s="7">
+        <f t="shared" si="0"/>
+        <v>0.33647223662121289</v>
+      </c>
+      <c r="H22" s="3">
+        <v>1.21</v>
+      </c>
+      <c r="I22" s="7">
+        <f t="shared" si="1"/>
+        <v>0.1906203596086497</v>
+      </c>
+      <c r="J22" s="3">
+        <v>1.63</v>
+      </c>
+      <c r="K22" s="7">
+        <f t="shared" si="2"/>
+        <v>0.48858001481867092</v>
+      </c>
+      <c r="L22" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>1.40 (1.21–1.63)</v>
+      </c>
+      <c r="M22" s="8">
+        <v>0.47199999999999998</v>
+      </c>
+      <c r="N22" s="2">
+        <v>24</v>
+      </c>
+      <c r="O22" s="9">
+        <v>28</v>
+      </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
@@ -1773,28 +2025,40 @@
       <c r="E23" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="8" t="e">
-        <f>LN(F23)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H23" s="3"/>
-      <c r="I23" s="8" t="e">
-        <f>LN(H23)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J23" s="3"/>
-      <c r="K23" s="8" t="e">
-        <f>LN(J23)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L23" s="8" t="str">
-        <f>TEXT(F23,"0.00") &amp; " (" &amp; TEXT(H23,"0.00") &amp; "–" &amp; TEXT(J23,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M23" s="9"/>
-      <c r="N23" s="2"/>
-      <c r="O23" s="10"/>
+      <c r="F23" s="3">
+        <v>1.34</v>
+      </c>
+      <c r="G23" s="7">
+        <f t="shared" si="0"/>
+        <v>0.29266961396282004</v>
+      </c>
+      <c r="H23" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="I23" s="7">
+        <f t="shared" si="1"/>
+        <v>9.5310179804324935E-2</v>
+      </c>
+      <c r="J23" s="3">
+        <v>1.62</v>
+      </c>
+      <c r="K23" s="7">
+        <f t="shared" si="2"/>
+        <v>0.48242614924429278</v>
+      </c>
+      <c r="L23" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>1.34 (1.10–1.62)</v>
+      </c>
+      <c r="M23" s="8">
+        <v>0.68</v>
+      </c>
+      <c r="N23" s="2">
+        <v>11</v>
+      </c>
+      <c r="O23" s="9">
+        <v>16</v>
+      </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
@@ -1812,28 +2076,40 @@
       <c r="E24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="8" t="e">
-        <f>LN(F24)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H24" s="3"/>
-      <c r="I24" s="8" t="e">
-        <f>LN(H24)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J24" s="3"/>
-      <c r="K24" s="8" t="e">
-        <f>LN(J24)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L24" s="8" t="str">
-        <f>TEXT(F24,"0.00") &amp; " (" &amp; TEXT(H24,"0.00") &amp; "–" &amp; TEXT(J24,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M24" s="9"/>
-      <c r="N24" s="2"/>
-      <c r="O24" s="10"/>
+      <c r="F24" s="3">
+        <v>1.38</v>
+      </c>
+      <c r="G24" s="7">
+        <f t="shared" si="0"/>
+        <v>0.32208349916911322</v>
+      </c>
+      <c r="H24" s="3">
+        <v>1.24</v>
+      </c>
+      <c r="I24" s="7">
+        <f t="shared" si="1"/>
+        <v>0.21511137961694549</v>
+      </c>
+      <c r="J24" s="3">
+        <v>1.55</v>
+      </c>
+      <c r="K24" s="7">
+        <f t="shared" si="2"/>
+        <v>0.43825493093115531</v>
+      </c>
+      <c r="L24" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>1.38 (1.24–1.55)</v>
+      </c>
+      <c r="M24" s="8">
+        <v>0</v>
+      </c>
+      <c r="N24" s="2">
+        <v>4</v>
+      </c>
+      <c r="O24" s="9">
+        <v>7</v>
+      </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
@@ -1851,28 +2127,40 @@
       <c r="E25" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F25" s="1"/>
-      <c r="G25" s="8" t="e">
-        <f>LN(F25)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H25" s="3"/>
-      <c r="I25" s="8" t="e">
-        <f>LN(H25)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J25" s="1"/>
-      <c r="K25" s="8" t="e">
-        <f>LN(J25)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L25" s="8" t="str">
-        <f>TEXT(F25,"0.00") &amp; " (" &amp; TEXT(H25,"0.00") &amp; "–" &amp; TEXT(J25,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M25" s="9"/>
-      <c r="N25" s="1"/>
-      <c r="O25" s="10"/>
+      <c r="F25" s="1">
+        <v>1.29</v>
+      </c>
+      <c r="G25" s="7">
+        <f t="shared" si="0"/>
+        <v>0.25464221837358075</v>
+      </c>
+      <c r="H25" s="3">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="I25" s="7">
+        <f t="shared" si="1"/>
+        <v>0.12221763272424911</v>
+      </c>
+      <c r="J25" s="1">
+        <v>1.48</v>
+      </c>
+      <c r="K25" s="7">
+        <f t="shared" si="2"/>
+        <v>0.39204208777602367</v>
+      </c>
+      <c r="L25" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>1.29 (1.13–1.48)</v>
+      </c>
+      <c r="M25" s="8">
+        <v>0.56599999999999995</v>
+      </c>
+      <c r="N25" s="1">
+        <v>12</v>
+      </c>
+      <c r="O25" s="9">
+        <v>17</v>
+      </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
@@ -1890,28 +2178,40 @@
       <c r="E26" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F26" s="1"/>
-      <c r="G26" s="8" t="e">
-        <f>LN(F26)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H26" s="3"/>
-      <c r="I26" s="8" t="e">
-        <f>LN(H26)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J26" s="1"/>
-      <c r="K26" s="8" t="e">
-        <f>LN(J26)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L26" s="8" t="str">
-        <f>TEXT(F26,"0.00") &amp; " (" &amp; TEXT(H26,"0.00") &amp; "–" &amp; TEXT(J26,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M26" s="9"/>
-      <c r="N26" s="1"/>
-      <c r="O26" s="10"/>
+      <c r="F26" s="1">
+        <v>1.42</v>
+      </c>
+      <c r="G26" s="7">
+        <f t="shared" si="0"/>
+        <v>0.35065687161316933</v>
+      </c>
+      <c r="H26" s="3">
+        <v>1.27</v>
+      </c>
+      <c r="I26" s="7">
+        <f t="shared" si="1"/>
+        <v>0.23901690047049992</v>
+      </c>
+      <c r="J26" s="1">
+        <v>1.59</v>
+      </c>
+      <c r="K26" s="7">
+        <f t="shared" si="2"/>
+        <v>0.46373401623214022</v>
+      </c>
+      <c r="L26" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>1.42 (1.27–1.59)</v>
+      </c>
+      <c r="M26" s="8">
+        <v>0.68200000000000005</v>
+      </c>
+      <c r="N26" s="1">
+        <v>35</v>
+      </c>
+      <c r="O26" s="9">
+        <v>67</v>
+      </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
@@ -1929,28 +2229,40 @@
       <c r="E27" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F27" s="1"/>
-      <c r="G27" s="8" t="e">
-        <f>LN(F27)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H27" s="3"/>
-      <c r="I27" s="8" t="e">
-        <f>LN(H27)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J27" s="1"/>
-      <c r="K27" s="8" t="e">
-        <f>LN(J27)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L27" s="8" t="str">
-        <f>TEXT(F27,"0.00") &amp; " (" &amp; TEXT(H27,"0.00") &amp; "–" &amp; TEXT(J27,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M27" s="9"/>
-      <c r="N27" s="1"/>
-      <c r="O27" s="10"/>
+      <c r="F27" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="G27" s="7">
+        <f t="shared" si="0"/>
+        <v>0.41210965082683298</v>
+      </c>
+      <c r="H27" s="3">
+        <v>1.31</v>
+      </c>
+      <c r="I27" s="7">
+        <f t="shared" si="1"/>
+        <v>0.27002713721306021</v>
+      </c>
+      <c r="J27" s="1">
+        <v>1.74</v>
+      </c>
+      <c r="K27" s="7">
+        <f t="shared" si="2"/>
+        <v>0.55388511322643763</v>
+      </c>
+      <c r="L27" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>1.51 (1.31–1.74)</v>
+      </c>
+      <c r="M27" s="8">
+        <v>0.27300000000000002</v>
+      </c>
+      <c r="N27" s="1">
+        <v>16</v>
+      </c>
+      <c r="O27" s="9">
+        <v>28</v>
+      </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
@@ -1968,28 +2280,40 @@
       <c r="E28" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F28" s="1"/>
-      <c r="G28" s="8" t="e">
-        <f>LN(F28)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H28" s="3"/>
-      <c r="I28" s="8" t="e">
-        <f>LN(H28)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J28" s="1"/>
-      <c r="K28" s="8" t="e">
-        <f>LN(J28)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L28" s="8" t="str">
-        <f>TEXT(F28,"0.00") &amp; " (" &amp; TEXT(H28,"0.00") &amp; "–" &amp; TEXT(J28,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M28" s="9"/>
-      <c r="N28" s="1"/>
-      <c r="O28" s="10"/>
+      <c r="F28" s="1">
+        <v>1.35</v>
+      </c>
+      <c r="G28" s="7">
+        <f t="shared" si="0"/>
+        <v>0.30010459245033816</v>
+      </c>
+      <c r="H28" s="3">
+        <v>1.23</v>
+      </c>
+      <c r="I28" s="7">
+        <f t="shared" si="1"/>
+        <v>0.20701416938432612</v>
+      </c>
+      <c r="J28" s="1">
+        <v>1.48</v>
+      </c>
+      <c r="K28" s="7">
+        <f t="shared" si="2"/>
+        <v>0.39204208777602367</v>
+      </c>
+      <c r="L28" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>1.35 (1.23–1.48)</v>
+      </c>
+      <c r="M28" s="8">
+        <v>0.39100000000000001</v>
+      </c>
+      <c r="N28" s="1">
+        <v>36</v>
+      </c>
+      <c r="O28" s="9">
+        <v>68</v>
+      </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
@@ -2007,28 +2331,40 @@
       <c r="E29" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8" t="e">
-        <f>LN(F29)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8" t="e">
-        <f>LN(H29)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J29" s="8"/>
-      <c r="K29" s="8" t="e">
-        <f>LN(J29)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L29" s="8" t="str">
-        <f>TEXT(F29,"0.00") &amp; " (" &amp; TEXT(H29,"0.00") &amp; "–" &amp; TEXT(J29,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M29" s="9"/>
-      <c r="N29" s="2"/>
-      <c r="O29" s="10"/>
+      <c r="F29" s="7">
+        <v>1.25</v>
+      </c>
+      <c r="G29" s="7">
+        <f t="shared" si="0"/>
+        <v>0.22314355131420976</v>
+      </c>
+      <c r="H29" s="7">
+        <v>0.92</v>
+      </c>
+      <c r="I29" s="7">
+        <f t="shared" si="1"/>
+        <v>-8.3381608939051013E-2</v>
+      </c>
+      <c r="J29" s="7">
+        <v>1.69</v>
+      </c>
+      <c r="K29" s="7">
+        <f t="shared" si="2"/>
+        <v>0.52472852893498212</v>
+      </c>
+      <c r="L29" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>1.25 (0.92–1.69)</v>
+      </c>
+      <c r="M29" s="8">
+        <v>0.82</v>
+      </c>
+      <c r="N29" s="2">
+        <v>5</v>
+      </c>
+      <c r="O29" s="9">
+        <v>6</v>
+      </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
@@ -2046,28 +2382,40 @@
       <c r="E30" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8" t="e">
-        <f>LN(F30)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H30" s="8"/>
-      <c r="I30" s="8" t="e">
-        <f>LN(H30)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J30" s="8"/>
-      <c r="K30" s="8" t="e">
-        <f>LN(J30)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L30" s="8" t="str">
-        <f>TEXT(F30,"0.00") &amp; " (" &amp; TEXT(H30,"0.00") &amp; "–" &amp; TEXT(J30,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M30" s="9"/>
-      <c r="N30" s="2"/>
-      <c r="O30" s="10"/>
+      <c r="F30" s="7">
+        <v>0.98</v>
+      </c>
+      <c r="G30" s="7">
+        <f t="shared" si="0"/>
+        <v>-2.0202707317519466E-2</v>
+      </c>
+      <c r="H30" s="7">
+        <v>0.83</v>
+      </c>
+      <c r="I30" s="7">
+        <f t="shared" si="1"/>
+        <v>-0.18632957819149348</v>
+      </c>
+      <c r="J30" s="7">
+        <v>1.17</v>
+      </c>
+      <c r="K30" s="7">
+        <f t="shared" si="2"/>
+        <v>0.15700374880966469</v>
+      </c>
+      <c r="L30" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>0.98 (0.83–1.17)</v>
+      </c>
+      <c r="M30" s="8">
+        <v>0.41699999999999998</v>
+      </c>
+      <c r="N30" s="2">
+        <v>3</v>
+      </c>
+      <c r="O30" s="9">
+        <v>4</v>
+      </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
@@ -2085,110 +2433,146 @@
       <c r="E31" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F31" s="3"/>
-      <c r="G31" s="8" t="e">
+      <c r="F31" s="3">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="G31" s="7">
         <f>LN(F31)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H31" s="3"/>
-      <c r="I31" s="8" t="e">
-        <f>LN(H31)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J31" s="3"/>
-      <c r="K31" s="8" t="e">
-        <f>LN(J31)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L31" s="8" t="str">
-        <f>TEXT(F31,"0.00") &amp; " (" &amp; TEXT(H31,"0.00") &amp; "–" &amp; TEXT(J31,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M31" s="9"/>
-      <c r="N31" s="1"/>
-      <c r="O31" s="10"/>
+        <v>0.10436001532424286</v>
+      </c>
+      <c r="H31" s="3">
+        <v>0.86</v>
+      </c>
+      <c r="I31" s="7">
+        <f t="shared" si="1"/>
+        <v>-0.15082288973458366</v>
+      </c>
+      <c r="J31" s="3">
+        <v>1.45</v>
+      </c>
+      <c r="K31" s="7">
+        <f t="shared" si="2"/>
+        <v>0.37156355643248301</v>
+      </c>
+      <c r="L31" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>1.11 (0.86–1.45)</v>
+      </c>
+      <c r="M31" s="8">
+        <v>0.78700000000000003</v>
+      </c>
+      <c r="N31" s="1">
+        <v>5</v>
+      </c>
+      <c r="O31" s="9">
+        <v>8</v>
+      </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B32" t="s">
         <v>19</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8" t="e">
+      <c r="F32" s="7">
+        <v>1.4</v>
+      </c>
+      <c r="G32" s="7">
         <f>LN(F32)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H32" s="8"/>
-      <c r="I32" s="8" t="e">
+        <v>0.33647223662121289</v>
+      </c>
+      <c r="H32" s="7">
+        <v>0.85</v>
+      </c>
+      <c r="I32" s="7">
         <f>LN(H32)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J32" s="8"/>
-      <c r="K32" s="8" t="e">
+        <v>-0.16251892949777494</v>
+      </c>
+      <c r="J32" s="7">
+        <v>2.31</v>
+      </c>
+      <c r="K32" s="7">
         <f>LN(J32)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L32" s="8" t="str">
+        <v>0.83724752453370221</v>
+      </c>
+      <c r="L32" s="7" t="str">
         <f>TEXT(F32,"0.00") &amp; " (" &amp; TEXT(H32,"0.00") &amp; "–" &amp; TEXT(J32,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M32" s="9"/>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
+        <v>1.40 (0.85–2.31)</v>
+      </c>
+      <c r="M32" s="8">
+        <v>0.872</v>
+      </c>
+      <c r="N32" s="2">
+        <v>3</v>
+      </c>
+      <c r="O32" s="9">
+        <v>3</v>
+      </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B33" t="s">
         <v>19</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F33" s="3"/>
-      <c r="G33" s="8" t="e">
+        <v>8</v>
+      </c>
+      <c r="F33" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G33" s="7">
         <f>LN(F33)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H33" s="3"/>
-      <c r="I33" s="8" t="e">
+        <v>9.5310179804324935E-2</v>
+      </c>
+      <c r="H33" s="7">
+        <v>0.84</v>
+      </c>
+      <c r="I33" s="7">
         <f>LN(H33)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J33" s="3"/>
-      <c r="K33" s="8" t="e">
+        <v>-0.1743533871447778</v>
+      </c>
+      <c r="J33" s="7">
+        <v>1.43</v>
+      </c>
+      <c r="K33" s="7">
         <f>LN(J33)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L33" s="8" t="str">
+        <v>0.35767444427181588</v>
+      </c>
+      <c r="L33" s="7" t="str">
         <f>TEXT(F33,"0.00") &amp; " (" &amp; TEXT(H33,"0.00") &amp; "–" &amp; TEXT(J33,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M33" s="9"/>
-      <c r="N33" s="2"/>
-      <c r="O33" s="10"/>
+        <v>1.10 (0.84–1.43)</v>
+      </c>
+      <c r="M33" s="8">
+        <v>0.70799999999999996</v>
+      </c>
+      <c r="N33" s="2">
+        <v>3</v>
+      </c>
+      <c r="O33" s="9">
+        <v>3</v>
+      </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B34" t="s">
         <v>19</v>
@@ -2200,151 +2584,199 @@
         <v>22</v>
       </c>
       <c r="E34" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F34" s="7">
+        <v>1.06</v>
+      </c>
+      <c r="G34" s="7">
+        <f t="shared" si="0"/>
+        <v>5.8268908123975824E-2</v>
+      </c>
+      <c r="H34" s="7">
+        <v>0.82</v>
+      </c>
+      <c r="I34" s="7">
+        <f t="shared" si="1"/>
+        <v>-0.19845093872383832</v>
+      </c>
+      <c r="J34" s="7">
+        <v>1.37</v>
+      </c>
+      <c r="K34" s="7">
+        <f t="shared" si="2"/>
+        <v>0.3148107398400336</v>
+      </c>
+      <c r="L34" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>1.06 (0.82–1.37)</v>
+      </c>
+      <c r="M34" s="8">
+        <v>0.65400000000000003</v>
+      </c>
+      <c r="N34" s="2">
         <v>8</v>
       </c>
-      <c r="F34" s="3"/>
-      <c r="G34" s="8" t="e">
-        <f>LN(F34)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H34" s="3"/>
-      <c r="I34" s="8" t="e">
-        <f>LN(H34)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J34" s="3"/>
-      <c r="K34" s="8" t="e">
-        <f>LN(J34)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L34" s="8" t="str">
-        <f>TEXT(F34,"0.00") &amp; " (" &amp; TEXT(H34,"0.00") &amp; "–" &amp; TEXT(J34,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M34" s="9"/>
-      <c r="N34" s="2"/>
-      <c r="O34" s="10"/>
+      <c r="O34" s="2">
+        <v>20</v>
+      </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B35" t="s">
         <v>19</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8" t="e">
-        <f>LN(F35)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H35" s="8"/>
-      <c r="I35" s="8" t="e">
-        <f>LN(H35)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J35" s="8"/>
-      <c r="K35" s="8" t="e">
-        <f>LN(J35)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L35" s="8" t="str">
-        <f>TEXT(F35,"0.00") &amp; " (" &amp; TEXT(H35,"0.00") &amp; "–" &amp; TEXT(J35,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M35" s="9"/>
-      <c r="N35" s="2"/>
-      <c r="O35" s="10"/>
+        <v>10</v>
+      </c>
+      <c r="F35" s="3">
+        <v>0.98</v>
+      </c>
+      <c r="G35" s="7">
+        <f t="shared" si="0"/>
+        <v>-2.0202707317519466E-2</v>
+      </c>
+      <c r="H35" s="3">
+        <v>0.81</v>
+      </c>
+      <c r="I35" s="7">
+        <f t="shared" si="1"/>
+        <v>-0.21072103131565253</v>
+      </c>
+      <c r="J35" s="3">
+        <v>1.19</v>
+      </c>
+      <c r="K35" s="7">
+        <f t="shared" si="2"/>
+        <v>0.17395330712343798</v>
+      </c>
+      <c r="L35" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>0.98 (0.81–1.19)</v>
+      </c>
+      <c r="M35" s="8">
+        <v>0.56100000000000005</v>
+      </c>
+      <c r="N35" s="2">
+        <v>6</v>
+      </c>
+      <c r="O35" s="9">
+        <v>12</v>
+      </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B36" t="s">
         <v>19</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8" t="e">
-        <f>LN(F36)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H36" s="8"/>
-      <c r="I36" s="8" t="e">
-        <f>LN(H36)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J36" s="8"/>
-      <c r="K36" s="8" t="e">
-        <f>LN(J36)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L36" s="8" t="str">
-        <f>TEXT(F36,"0.00") &amp; " (" &amp; TEXT(H36,"0.00") &amp; "–" &amp; TEXT(J36,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M36" s="9"/>
-      <c r="N36" s="2"/>
-      <c r="O36" s="10"/>
+      <c r="F36" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G36" s="7">
+        <f t="shared" ref="G36:G69" si="4">LN(F36)</f>
+        <v>9.5310179804324935E-2</v>
+      </c>
+      <c r="H36" s="3">
+        <v>0.87</v>
+      </c>
+      <c r="I36" s="7">
+        <f t="shared" ref="I36:I69" si="5">LN(H36)</f>
+        <v>-0.13926206733350766</v>
+      </c>
+      <c r="J36" s="3">
+        <v>1.39</v>
+      </c>
+      <c r="K36" s="7">
+        <f t="shared" ref="K36:K69" si="6">LN(J36)</f>
+        <v>0.3293037471426003</v>
+      </c>
+      <c r="L36" s="7" t="str">
+        <f t="shared" ref="L36:L69" si="7">TEXT(F36,"0.00") &amp; " (" &amp; TEXT(H36,"0.00") &amp; "–" &amp; TEXT(J36,"0.00") &amp; ")"</f>
+        <v>1.10 (0.87–1.39)</v>
+      </c>
+      <c r="M36" s="8">
+        <v>0.63400000000000001</v>
+      </c>
+      <c r="N36" s="2">
+        <v>9</v>
+      </c>
+      <c r="O36" s="9">
+        <v>22</v>
+      </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B37" t="s">
         <v>19</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F37" s="3"/>
-      <c r="G37" s="8" t="e">
+        <v>9</v>
+      </c>
+      <c r="F37" s="7">
+        <v>0.87</v>
+      </c>
+      <c r="G37" s="7">
         <f>LN(F37)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H37" s="3"/>
-      <c r="I37" s="8" t="e">
+        <v>-0.13926206733350766</v>
+      </c>
+      <c r="H37" s="7">
+        <v>0.77</v>
+      </c>
+      <c r="I37" s="7">
         <f>LN(H37)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J37" s="3"/>
-      <c r="K37" s="8" t="e">
+        <v>-0.26136476413440751</v>
+      </c>
+      <c r="J37" s="7">
+        <v>0.98</v>
+      </c>
+      <c r="K37" s="7">
         <f>LN(J37)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L37" s="8" t="str">
+        <v>-2.0202707317519466E-2</v>
+      </c>
+      <c r="L37" s="7" t="str">
         <f>TEXT(F37,"0.00") &amp; " (" &amp; TEXT(H37,"0.00") &amp; "–" &amp; TEXT(J37,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M37" s="9"/>
-      <c r="N37" s="2"/>
-      <c r="O37" s="10"/>
+        <v>0.87 (0.77–0.98)</v>
+      </c>
+      <c r="M37" s="8">
+        <v>0</v>
+      </c>
+      <c r="N37" s="2">
+        <v>3</v>
+      </c>
+      <c r="O37" s="9">
+        <v>5</v>
+      </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B38" t="s">
         <v>19</v>
@@ -2358,32 +2790,44 @@
       <c r="E38" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F38" s="8"/>
-      <c r="G38" s="8" t="e">
+      <c r="F38" s="7">
+        <v>0.87</v>
+      </c>
+      <c r="G38" s="7">
         <f>LN(F38)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H38" s="8"/>
-      <c r="I38" s="8" t="e">
+        <v>-0.13926206733350766</v>
+      </c>
+      <c r="H38" s="7">
+        <v>0.77</v>
+      </c>
+      <c r="I38" s="7">
         <f>LN(H38)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J38" s="8"/>
-      <c r="K38" s="8" t="e">
+        <v>-0.26136476413440751</v>
+      </c>
+      <c r="J38" s="7">
+        <v>0.99</v>
+      </c>
+      <c r="K38" s="7">
         <f>LN(J38)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L38" s="8" t="str">
+        <v>-1.0050335853501451E-2</v>
+      </c>
+      <c r="L38" s="7" t="str">
         <f>TEXT(F38,"0.00") &amp; " (" &amp; TEXT(H38,"0.00") &amp; "–" &amp; TEXT(J38,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M38" s="9"/>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
+        <v>0.87 (0.77–0.99)</v>
+      </c>
+      <c r="M38" s="8">
+        <v>0</v>
+      </c>
+      <c r="N38" s="2">
+        <v>3</v>
+      </c>
+      <c r="O38" s="9">
+        <v>5</v>
+      </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B39" t="s">
         <v>19</v>
@@ -2395,40 +2839,52 @@
         <v>22</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F39" s="3"/>
-      <c r="G39" s="8" t="e">
+        <v>9</v>
+      </c>
+      <c r="F39" s="7">
+        <v>0.85</v>
+      </c>
+      <c r="G39" s="7">
         <f>LN(F39)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H39" s="3"/>
-      <c r="I39" s="8" t="e">
+        <v>-0.16251892949777494</v>
+      </c>
+      <c r="H39" s="7">
+        <v>0.66</v>
+      </c>
+      <c r="I39" s="7">
         <f>LN(H39)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J39" s="3"/>
-      <c r="K39" s="8" t="e">
+        <v>-0.41551544396166579</v>
+      </c>
+      <c r="J39" s="7">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="K39" s="7">
         <f>LN(J39)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L39" s="8" t="str">
+        <v>0.10436001532424286</v>
+      </c>
+      <c r="L39" s="7" t="str">
         <f>TEXT(F39,"0.00") &amp; " (" &amp; TEXT(H39,"0.00") &amp; "–" &amp; TEXT(J39,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M39" s="9"/>
-      <c r="N39" s="2"/>
-      <c r="O39" s="10"/>
+        <v>0.85 (0.66–1.11)</v>
+      </c>
+      <c r="M39" s="8">
+        <v>0.78</v>
+      </c>
+      <c r="N39" s="2">
+        <v>4</v>
+      </c>
+      <c r="O39" s="9">
+        <v>5</v>
+      </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B40" t="s">
         <v>19</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>22</v>
@@ -2436,149 +2892,197 @@
       <c r="E40" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F40" s="3"/>
-      <c r="G40" s="8" t="e">
+      <c r="F40" s="7">
+        <v>0.84</v>
+      </c>
+      <c r="G40" s="7">
         <f>LN(F40)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H40" s="3"/>
-      <c r="I40" s="8" t="e">
+        <v>-0.1743533871447778</v>
+      </c>
+      <c r="H40" s="7">
+        <v>0.67</v>
+      </c>
+      <c r="I40" s="7">
         <f>LN(H40)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J40" s="3"/>
-      <c r="K40" s="8" t="e">
+        <v>-0.40047756659712525</v>
+      </c>
+      <c r="J40" s="7">
+        <v>1.07</v>
+      </c>
+      <c r="K40" s="7">
         <f>LN(J40)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L40" s="8" t="str">
+        <v>6.7658648473814864E-2</v>
+      </c>
+      <c r="L40" s="7" t="str">
         <f>TEXT(F40,"0.00") &amp; " (" &amp; TEXT(H40,"0.00") &amp; "–" &amp; TEXT(J40,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M40" s="9"/>
-      <c r="N40" s="2"/>
-      <c r="O40" s="10"/>
+        <v>0.84 (0.67–1.07)</v>
+      </c>
+      <c r="M40" s="8">
+        <v>0.71099999999999997</v>
+      </c>
+      <c r="N40" s="2">
+        <v>4</v>
+      </c>
+      <c r="O40" s="9">
+        <v>5</v>
+      </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B41" t="s">
         <v>19</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F41" s="3"/>
-      <c r="G41" s="8" t="e">
-        <f>LN(F41)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H41" s="3"/>
-      <c r="I41" s="8" t="e">
-        <f>LN(H41)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J41" s="3"/>
-      <c r="K41" s="8" t="e">
-        <f>LN(J41)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L41" s="8" t="str">
-        <f>TEXT(F41,"0.00") &amp; " (" &amp; TEXT(H41,"0.00") &amp; "–" &amp; TEXT(J41,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M41" s="9"/>
-      <c r="N41" s="2"/>
-      <c r="O41" s="10"/>
+        <v>9</v>
+      </c>
+      <c r="F41" s="3">
+        <v>1.01</v>
+      </c>
+      <c r="G41" s="7">
+        <f t="shared" si="4"/>
+        <v>9.950330853168092E-3</v>
+      </c>
+      <c r="H41" s="3">
+        <v>0.68</v>
+      </c>
+      <c r="I41" s="7">
+        <f t="shared" si="5"/>
+        <v>-0.38566248081198462</v>
+      </c>
+      <c r="J41" s="3">
+        <v>1.51</v>
+      </c>
+      <c r="K41" s="7">
+        <f t="shared" si="6"/>
+        <v>0.41210965082683298</v>
+      </c>
+      <c r="L41" s="7" t="str">
+        <f t="shared" ref="L41" si="8">TEXT(F41,"0.00") &amp; " (" &amp; TEXT(H41,"0.00") &amp; "–" &amp; TEXT(J41,"0.00") &amp; ")"</f>
+        <v>1.01 (0.68–1.51)</v>
+      </c>
+      <c r="M41" s="8">
+        <v>0.80600000000000005</v>
+      </c>
+      <c r="N41" s="2">
+        <v>5</v>
+      </c>
+      <c r="O41" s="9">
+        <v>6</v>
+      </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F42" s="8"/>
-      <c r="G42" s="8" t="e">
-        <f>LN(F42)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H42" s="8"/>
-      <c r="I42" s="8" t="e">
-        <f>LN(H42)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J42" s="8"/>
-      <c r="K42" s="8" t="e">
-        <f>LN(J42)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L42" s="8" t="str">
-        <f>TEXT(F42,"0.00") &amp; " (" &amp; TEXT(H42,"0.00") &amp; "–" &amp; TEXT(J42,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M42" s="9"/>
-      <c r="N42" s="1"/>
-      <c r="O42" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0.97</v>
+      </c>
+      <c r="G42" s="7">
+        <f t="shared" si="4"/>
+        <v>-3.0459207484708574E-2</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="I42" s="7">
+        <f t="shared" si="5"/>
+        <v>-0.2876820724517809</v>
+      </c>
+      <c r="J42" s="3">
+        <v>1.25</v>
+      </c>
+      <c r="K42" s="7">
+        <f t="shared" si="6"/>
+        <v>0.22314355131420976</v>
+      </c>
+      <c r="L42" s="7" t="str">
+        <f t="shared" si="7"/>
+        <v>0.97 (0.75–1.25)</v>
+      </c>
+      <c r="M42" s="8">
+        <v>0.69499999999999995</v>
+      </c>
+      <c r="N42" s="2">
+        <v>5</v>
+      </c>
+      <c r="O42" s="9">
+        <v>6</v>
+      </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F43" s="8"/>
-      <c r="G43" s="8" t="e">
+        <v>8</v>
+      </c>
+      <c r="F43" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G43" s="7">
         <f>LN(F43)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H43" s="8"/>
-      <c r="I43" s="8" t="e">
+        <v>9.5310179804324935E-2</v>
+      </c>
+      <c r="H43" s="3">
+        <v>0.81</v>
+      </c>
+      <c r="I43" s="7">
         <f>LN(H43)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J43" s="8"/>
-      <c r="K43" s="8" t="e">
+        <v>-0.21072103131565253</v>
+      </c>
+      <c r="J43" s="3">
+        <v>1.49</v>
+      </c>
+      <c r="K43" s="7">
         <f>LN(J43)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L43" s="8" t="str">
+        <v>0.39877611995736778</v>
+      </c>
+      <c r="L43" s="7" t="str">
         <f>TEXT(F43,"0.00") &amp; " (" &amp; TEXT(H43,"0.00") &amp; "–" &amp; TEXT(J43,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M43" s="9"/>
-      <c r="N43" s="1"/>
-      <c r="O43" s="1"/>
+        <v>1.10 (0.81–1.49)</v>
+      </c>
+      <c r="M43" s="8">
+        <v>0.77500000000000002</v>
+      </c>
+      <c r="N43" s="2">
+        <v>6</v>
+      </c>
+      <c r="O43" s="9">
+        <v>8</v>
+      </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B44" t="s">
         <v>24</v>
@@ -2590,79 +3094,103 @@
         <v>21</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F44" s="3"/>
-      <c r="G44" s="8" t="e">
-        <f>LN(F44)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H44" s="3"/>
-      <c r="I44" s="8" t="e">
-        <f>LN(H44)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J44" s="3"/>
-      <c r="K44" s="8" t="e">
-        <f>LN(J44)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L44" s="8" t="str">
-        <f>TEXT(F44,"0.00") &amp; " (" &amp; TEXT(H44,"0.00") &amp; "–" &amp; TEXT(J44,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M44" s="9"/>
-      <c r="N44" s="1"/>
-      <c r="O44" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="F44" s="7">
+        <v>0.82</v>
+      </c>
+      <c r="G44" s="7">
+        <f t="shared" si="4"/>
+        <v>-0.19845093872383832</v>
+      </c>
+      <c r="H44" s="7">
+        <v>0.68</v>
+      </c>
+      <c r="I44" s="7">
+        <f t="shared" si="5"/>
+        <v>-0.38566248081198462</v>
+      </c>
+      <c r="J44" s="7">
+        <v>0.99</v>
+      </c>
+      <c r="K44" s="7">
+        <f t="shared" si="6"/>
+        <v>-1.0050335853501451E-2</v>
+      </c>
+      <c r="L44" s="7" t="str">
+        <f t="shared" si="7"/>
+        <v>0.82 (0.68–0.99)</v>
+      </c>
+      <c r="M44" s="8">
+        <v>0</v>
+      </c>
+      <c r="N44" s="1">
+        <v>6</v>
+      </c>
+      <c r="O44" s="1">
+        <v>14</v>
+      </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B45" t="s">
         <v>24</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F45" s="3"/>
-      <c r="G45" s="8" t="e">
-        <f>LN(F45)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H45" s="3"/>
-      <c r="I45" s="8" t="e">
-        <f>LN(H45)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J45" s="3"/>
-      <c r="K45" s="8" t="e">
-        <f>LN(J45)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L45" s="8" t="str">
-        <f>TEXT(F45,"0.00") &amp; " (" &amp; TEXT(H45,"0.00") &amp; "–" &amp; TEXT(J45,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M45" s="9"/>
-      <c r="N45" s="1"/>
-      <c r="O45" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="F45" s="7">
+        <v>0.78</v>
+      </c>
+      <c r="G45" s="7">
+        <f t="shared" si="4"/>
+        <v>-0.24846135929849961</v>
+      </c>
+      <c r="H45" s="7">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="I45" s="7">
+        <f t="shared" si="5"/>
+        <v>-0.57981849525294205</v>
+      </c>
+      <c r="J45" s="7">
+        <v>1.08</v>
+      </c>
+      <c r="K45" s="7">
+        <f t="shared" si="6"/>
+        <v>7.6961041136128394E-2</v>
+      </c>
+      <c r="L45" s="7" t="str">
+        <f t="shared" si="7"/>
+        <v>0.78 (0.56–1.08)</v>
+      </c>
+      <c r="M45" s="8">
+        <v>0.49</v>
+      </c>
+      <c r="N45" s="1">
+        <v>5</v>
+      </c>
+      <c r="O45" s="1">
+        <v>14</v>
+      </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B46" t="s">
         <v>24</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>21</v>
@@ -2670,32 +3198,44 @@
       <c r="E46" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F46" s="3"/>
-      <c r="G46" s="8" t="e">
-        <f>LN(F46)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H46" s="3"/>
-      <c r="I46" s="8" t="e">
-        <f>LN(H46)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J46" s="3"/>
-      <c r="K46" s="8" t="e">
-        <f>LN(J46)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L46" s="8" t="str">
-        <f>TEXT(F46,"0.00") &amp; " (" &amp; TEXT(H46,"0.00") &amp; "–" &amp; TEXT(J46,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M46" s="9"/>
-      <c r="N46" s="1"/>
-      <c r="O46" s="1"/>
+      <c r="F46" s="3">
+        <v>0.78</v>
+      </c>
+      <c r="G46" s="7">
+        <f t="shared" si="4"/>
+        <v>-0.24846135929849961</v>
+      </c>
+      <c r="H46" s="3">
+        <v>0.64</v>
+      </c>
+      <c r="I46" s="7">
+        <f t="shared" si="5"/>
+        <v>-0.44628710262841947</v>
+      </c>
+      <c r="J46" s="3">
+        <v>0.94</v>
+      </c>
+      <c r="K46" s="7">
+        <f t="shared" si="6"/>
+        <v>-6.1875403718087529E-2</v>
+      </c>
+      <c r="L46" s="7" t="str">
+        <f t="shared" si="7"/>
+        <v>0.78 (0.64–0.94)</v>
+      </c>
+      <c r="M46" s="8">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="N46" s="1">
+        <v>7</v>
+      </c>
+      <c r="O46" s="1">
+        <v>17</v>
+      </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B47" t="s">
         <v>24</v>
@@ -2709,32 +3249,44 @@
       <c r="E47" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F47" s="8"/>
-      <c r="G47" s="8" t="e">
+      <c r="F47" s="7">
+        <v>0.72</v>
+      </c>
+      <c r="G47" s="7">
         <f>LN(F47)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H47" s="8"/>
-      <c r="I47" s="8" t="e">
+        <v>-0.3285040669720361</v>
+      </c>
+      <c r="H47" s="7">
+        <v>0.38</v>
+      </c>
+      <c r="I47" s="7">
         <f>LN(H47)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J47" s="8"/>
-      <c r="K47" s="8" t="e">
+        <v>-0.96758402626170559</v>
+      </c>
+      <c r="J47" s="7">
+        <v>1.4</v>
+      </c>
+      <c r="K47" s="7">
         <f>LN(J47)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L47" s="8" t="str">
+        <v>0.33647223662121289</v>
+      </c>
+      <c r="L47" s="7" t="str">
         <f>TEXT(F47,"0.00") &amp; " (" &amp; TEXT(H47,"0.00") &amp; "–" &amp; TEXT(J47,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M47" s="9"/>
-      <c r="N47" s="1"/>
-      <c r="O47" s="10"/>
+        <v>0.72 (0.38–1.40)</v>
+      </c>
+      <c r="M47" s="8">
+        <v>0</v>
+      </c>
+      <c r="N47" s="1">
+        <v>3</v>
+      </c>
+      <c r="O47" s="9">
+        <v>4</v>
+      </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B48" t="s">
         <v>24</v>
@@ -2746,79 +3298,103 @@
         <v>22</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F48" s="3"/>
-      <c r="G48" s="8" t="e">
+        <v>8</v>
+      </c>
+      <c r="F48" s="3">
+        <v>0.71</v>
+      </c>
+      <c r="G48" s="7">
         <f>LN(F48)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H48" s="3"/>
-      <c r="I48" s="8" t="e">
+        <v>-0.34249030894677601</v>
+      </c>
+      <c r="H48" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="I48" s="7">
         <f>LN(H48)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J48" s="3"/>
-      <c r="K48" s="8" t="e">
+        <v>-1.0498221244986778</v>
+      </c>
+      <c r="J48" s="3">
+        <v>1.45</v>
+      </c>
+      <c r="K48" s="7">
         <f>LN(J48)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L48" s="8" t="str">
+        <v>0.37156355643248301</v>
+      </c>
+      <c r="L48" s="7" t="str">
         <f>TEXT(F48,"0.00") &amp; " (" &amp; TEXT(H48,"0.00") &amp; "–" &amp; TEXT(J48,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M48" s="9"/>
-      <c r="N48" s="1"/>
-      <c r="O48" s="1"/>
+        <v>0.71 (0.35–1.45)</v>
+      </c>
+      <c r="M48" s="8">
+        <v>0</v>
+      </c>
+      <c r="N48" s="1">
+        <v>3</v>
+      </c>
+      <c r="O48" s="1">
+        <v>4</v>
+      </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B49" t="s">
         <v>24</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F49" s="3"/>
-      <c r="G49" s="8" t="e">
+      <c r="F49" s="3">
+        <v>0.83</v>
+      </c>
+      <c r="G49" s="7">
         <f>LN(F49)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H49" s="3"/>
-      <c r="I49" s="8" t="e">
+        <v>-0.18632957819149348</v>
+      </c>
+      <c r="H49" s="3">
+        <v>0.66</v>
+      </c>
+      <c r="I49" s="7">
         <f>LN(H49)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J49" s="3"/>
-      <c r="K49" s="8" t="e">
+        <v>-0.41551544396166579</v>
+      </c>
+      <c r="J49" s="3">
+        <v>1.05</v>
+      </c>
+      <c r="K49" s="7">
         <f>LN(J49)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L49" s="8" t="str">
+        <v>4.8790164169432049E-2</v>
+      </c>
+      <c r="L49" s="7" t="str">
         <f>TEXT(F49,"0.00") &amp; " (" &amp; TEXT(H49,"0.00") &amp; "–" &amp; TEXT(J49,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M49" s="9"/>
-      <c r="N49" s="1"/>
-      <c r="O49" s="1"/>
+        <v>0.83 (0.66–1.05)</v>
+      </c>
+      <c r="M49" s="8">
+        <v>0</v>
+      </c>
+      <c r="N49" s="1">
+        <v>3</v>
+      </c>
+      <c r="O49" s="1">
+        <v>3</v>
+      </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>21</v>
@@ -2826,38 +3402,50 @@
       <c r="E50" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F50" s="3"/>
-      <c r="G50" s="3" t="e">
-        <f>LN(F50)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H50" s="3"/>
-      <c r="I50" s="3" t="e">
-        <f>LN(H50)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J50" s="5"/>
-      <c r="K50" s="8" t="e">
-        <f>LN(J50)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L50" s="10" t="str">
-        <f>TEXT(F50,"0.00") &amp; " (" &amp; TEXT(H50,"0.00") &amp; "–" &amp; TEXT(J50,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M50" s="9"/>
-      <c r="N50" s="1"/>
-      <c r="O50" s="1"/>
+      <c r="F50" s="3">
+        <v>0.72</v>
+      </c>
+      <c r="G50" s="7">
+        <f t="shared" si="4"/>
+        <v>-0.3285040669720361</v>
+      </c>
+      <c r="H50" s="3">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="I50" s="7">
+        <f t="shared" si="5"/>
+        <v>-0.54472717544167215</v>
+      </c>
+      <c r="J50" s="3">
+        <v>0.91</v>
+      </c>
+      <c r="K50" s="7">
+        <f t="shared" si="6"/>
+        <v>-9.431067947124129E-2</v>
+      </c>
+      <c r="L50" s="7" t="str">
+        <f t="shared" si="7"/>
+        <v>0.72 (0.58–0.91)</v>
+      </c>
+      <c r="M50" s="8">
+        <v>0</v>
+      </c>
+      <c r="N50" s="1">
+        <v>5</v>
+      </c>
+      <c r="O50" s="1">
+        <v>10</v>
+      </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>21</v>
@@ -2865,38 +3453,50 @@
       <c r="E51" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F51" s="3"/>
-      <c r="G51" s="3" t="e">
-        <f>LN(F51)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H51" s="3"/>
-      <c r="I51" s="3" t="e">
-        <f>LN(H51)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J51" s="3"/>
-      <c r="K51" s="8" t="e">
-        <f>LN(J51)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L51" s="10" t="str">
-        <f>TEXT(F51,"0.00") &amp; " (" &amp; TEXT(H51,"0.00") &amp; "–" &amp; TEXT(J51,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M51" s="9"/>
-      <c r="N51" s="1"/>
-      <c r="O51" s="1"/>
+      <c r="F51" s="3">
+        <v>0.66</v>
+      </c>
+      <c r="G51" s="7">
+        <f t="shared" si="4"/>
+        <v>-0.41551544396166579</v>
+      </c>
+      <c r="H51" s="3">
+        <v>0.46</v>
+      </c>
+      <c r="I51" s="7">
+        <f t="shared" si="5"/>
+        <v>-0.77652878949899629</v>
+      </c>
+      <c r="J51" s="3">
+        <v>0.96</v>
+      </c>
+      <c r="K51" s="7">
+        <f t="shared" si="6"/>
+        <v>-4.0821994520255166E-2</v>
+      </c>
+      <c r="L51" s="7" t="str">
+        <f t="shared" ref="L51:L52" si="9">TEXT(F51,"0.00") &amp; " (" &amp; TEXT(H51,"0.00") &amp; "–" &amp; TEXT(J51,"0.00") &amp; ")"</f>
+        <v>0.66 (0.46–0.96)</v>
+      </c>
+      <c r="M51" s="8">
+        <v>0.50600000000000001</v>
+      </c>
+      <c r="N51" s="1">
+        <v>4</v>
+      </c>
+      <c r="O51" s="1">
+        <v>9</v>
+      </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>21</v>
@@ -2904,74 +3504,98 @@
       <c r="E52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F52" s="3"/>
-      <c r="G52" s="3" t="e">
-        <f>LN(F52)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H52" s="3"/>
-      <c r="I52" s="3" t="e">
-        <f>LN(H52)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J52" s="3"/>
-      <c r="K52" s="8" t="e">
-        <f>LN(J52)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L52" s="10" t="str">
-        <f>TEXT(F52,"0.00") &amp; " (" &amp; TEXT(H52,"0.00") &amp; "–" &amp; TEXT(J52,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M52" s="9"/>
-      <c r="N52" s="1"/>
-      <c r="O52" s="1"/>
+      <c r="F52" s="3">
+        <v>0.68</v>
+      </c>
+      <c r="G52" s="7">
+        <f t="shared" si="4"/>
+        <v>-0.38566248081198462</v>
+      </c>
+      <c r="H52" s="3">
+        <v>0.54</v>
+      </c>
+      <c r="I52" s="7">
+        <f t="shared" si="5"/>
+        <v>-0.61618613942381695</v>
+      </c>
+      <c r="J52" s="3">
+        <v>0.87</v>
+      </c>
+      <c r="K52" s="7">
+        <f t="shared" si="6"/>
+        <v>-0.13926206733350766</v>
+      </c>
+      <c r="L52" s="7" t="str">
+        <f t="shared" si="9"/>
+        <v>0.68 (0.54–0.87)</v>
+      </c>
+      <c r="M52" s="8">
+        <v>0</v>
+      </c>
+      <c r="N52" s="1">
+        <v>7</v>
+      </c>
+      <c r="O52" s="1">
+        <v>17</v>
+      </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B53" t="s">
         <v>25</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F53" s="3"/>
-      <c r="G53" s="3" t="e">
-        <f>LN(F53)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H53" s="3"/>
-      <c r="I53" s="3" t="e">
-        <f>LN(H53)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J53" s="3"/>
-      <c r="K53" s="8" t="e">
-        <f>LN(J53)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L53" s="10" t="str">
-        <f>TEXT(F53,"0.00") &amp; " (" &amp; TEXT(H53,"0.00") &amp; "–" &amp; TEXT(J53,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M53" s="9"/>
-      <c r="N53" s="1"/>
-      <c r="O53" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="F53" s="3">
+        <v>0.63</v>
+      </c>
+      <c r="G53" s="3">
+        <f t="shared" si="4"/>
+        <v>-0.46203545959655867</v>
+      </c>
+      <c r="H53" s="3">
+        <v>0.33</v>
+      </c>
+      <c r="I53" s="3">
+        <f t="shared" si="5"/>
+        <v>-1.1086626245216111</v>
+      </c>
+      <c r="J53" s="3">
+        <v>1.24</v>
+      </c>
+      <c r="K53" s="7">
+        <f t="shared" si="6"/>
+        <v>0.21511137961694549</v>
+      </c>
+      <c r="L53" s="9" t="str">
+        <f t="shared" si="7"/>
+        <v>0.63 (0.33–1.24)</v>
+      </c>
+      <c r="M53" s="8">
+        <v>0.70599999999999996</v>
+      </c>
+      <c r="N53" s="1">
+        <v>4</v>
+      </c>
+      <c r="O53" s="1">
+        <v>15</v>
+      </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>23</v>
@@ -2980,37 +3604,49 @@
         <v>21</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F54" s="8"/>
-      <c r="G54" s="8" t="e">
-        <f>LN(F54)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H54" s="8"/>
-      <c r="I54" s="8" t="e">
-        <f>LN(H54)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J54" s="8"/>
-      <c r="K54" s="8" t="e">
-        <f>LN(J54)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L54" s="8" t="str">
-        <f>TEXT(F54,"0.00") &amp; " (" &amp; TEXT(H54,"0.00") &amp; "–" &amp; TEXT(J54,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M54" s="9"/>
-      <c r="N54" s="1"/>
-      <c r="O54" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="F54" s="3">
+        <v>0.65</v>
+      </c>
+      <c r="G54" s="3">
+        <f t="shared" si="4"/>
+        <v>-0.43078291609245423</v>
+      </c>
+      <c r="H54" s="3">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="I54" s="3">
+        <f t="shared" si="5"/>
+        <v>-1.2729656758128873</v>
+      </c>
+      <c r="J54" s="3">
+        <v>1.49</v>
+      </c>
+      <c r="K54" s="7">
+        <f t="shared" si="6"/>
+        <v>0.39877611995736778</v>
+      </c>
+      <c r="L54" s="9" t="str">
+        <f t="shared" si="7"/>
+        <v>0.65 (0.28–1.49)</v>
+      </c>
+      <c r="M54" s="8">
+        <v>0.69799999999999995</v>
+      </c>
+      <c r="N54" s="1">
+        <v>3</v>
+      </c>
+      <c r="O54" s="1">
+        <v>14</v>
+      </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>23</v>
@@ -3021,35 +3657,47 @@
       <c r="E55" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F55" s="3"/>
-      <c r="G55" s="8" t="e">
-        <f>LN(F55)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H55" s="3"/>
-      <c r="I55" s="8" t="e">
-        <f>LN(H55)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J55" s="3"/>
-      <c r="K55" s="8" t="e">
-        <f>LN(J55)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L55" s="8" t="str">
-        <f>TEXT(F55,"0.00") &amp; " (" &amp; TEXT(H55,"0.00") &amp; "–" &amp; TEXT(J55,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M55" s="9"/>
-      <c r="N55" s="1"/>
-      <c r="O55" s="1"/>
+      <c r="F55" s="3">
+        <v>0.65</v>
+      </c>
+      <c r="G55" s="3">
+        <f t="shared" si="4"/>
+        <v>-0.43078291609245423</v>
+      </c>
+      <c r="H55" s="3">
+        <v>0.33</v>
+      </c>
+      <c r="I55" s="3">
+        <f t="shared" si="5"/>
+        <v>-1.1086626245216111</v>
+      </c>
+      <c r="J55" s="3">
+        <v>1.29</v>
+      </c>
+      <c r="K55" s="7">
+        <f t="shared" si="6"/>
+        <v>0.25464221837358075</v>
+      </c>
+      <c r="L55" s="9" t="str">
+        <f t="shared" si="7"/>
+        <v>0.65 (0.33–1.29)</v>
+      </c>
+      <c r="M55" s="8">
+        <v>0.67500000000000004</v>
+      </c>
+      <c r="N55" s="1">
+        <v>4</v>
+      </c>
+      <c r="O55" s="1">
+        <v>15</v>
+      </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>29</v>
@@ -3058,112 +3706,148 @@
         <v>21</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F56" s="3"/>
-      <c r="G56" s="8" t="e">
-        <f>LN(F56)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H56" s="3"/>
-      <c r="I56" s="8" t="e">
-        <f>LN(H56)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J56" s="3"/>
-      <c r="K56" s="8" t="e">
-        <f>LN(J56)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L56" s="8" t="str">
-        <f>TEXT(F56,"0.00") &amp; " (" &amp; TEXT(H56,"0.00") &amp; "–" &amp; TEXT(J56,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M56" s="9"/>
-      <c r="N56" s="1"/>
-      <c r="O56" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="F56" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="G56" s="3">
+        <f t="shared" si="4"/>
+        <v>-0.69314718055994529</v>
+      </c>
+      <c r="H56" s="3">
+        <v>0.33</v>
+      </c>
+      <c r="I56" s="3">
+        <f t="shared" si="5"/>
+        <v>-1.1086626245216111</v>
+      </c>
+      <c r="J56" s="3">
+        <v>0.76</v>
+      </c>
+      <c r="K56" s="7">
+        <f t="shared" si="6"/>
+        <v>-0.2744368457017603</v>
+      </c>
+      <c r="L56" s="9" t="str">
+        <f t="shared" si="7"/>
+        <v>0.50 (0.33–0.76)</v>
+      </c>
+      <c r="M56" s="8">
+        <v>0.74199999999999999</v>
+      </c>
+      <c r="N56" s="1">
+        <v>4</v>
+      </c>
+      <c r="O56" s="1">
+        <v>11</v>
+      </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F57" s="8"/>
-      <c r="G57" s="8" t="e">
+        <v>10</v>
+      </c>
+      <c r="F57" s="3">
+        <v>0.48</v>
+      </c>
+      <c r="G57" s="3">
         <f>LN(F57)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H57" s="8"/>
-      <c r="I57" s="8" t="e">
+        <v>-0.73396917508020043</v>
+      </c>
+      <c r="H57" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="I57" s="3">
         <f>LN(H57)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J57" s="8"/>
-      <c r="K57" s="8" t="e">
+        <v>-1.2039728043259361</v>
+      </c>
+      <c r="J57" s="3">
+        <v>0.77</v>
+      </c>
+      <c r="K57" s="7">
         <f>LN(J57)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L57" s="8" t="str">
+        <v>-0.26136476413440751</v>
+      </c>
+      <c r="L57" s="9" t="str">
         <f>TEXT(F57,"0.00") &amp; " (" &amp; TEXT(H57,"0.00") &amp; "–" &amp; TEXT(J57,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M57" s="9"/>
-      <c r="N57" s="1"/>
-      <c r="O57" s="10"/>
+        <v>0.48 (0.30–0.77)</v>
+      </c>
+      <c r="M57" s="8">
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="N57" s="1">
+        <v>3</v>
+      </c>
+      <c r="O57" s="1">
+        <v>10</v>
+      </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F58" s="3">
+        <v>0.49</v>
+      </c>
+      <c r="G58" s="3">
+        <f>LN(F58)</f>
+        <v>-0.71334988787746478</v>
+      </c>
+      <c r="H58" s="3">
+        <v>0.31</v>
+      </c>
+      <c r="I58" s="3">
+        <f>LN(H58)</f>
+        <v>-1.1711829815029451</v>
+      </c>
+      <c r="J58" s="3">
+        <v>0.77</v>
+      </c>
+      <c r="K58" s="7">
+        <f>LN(J58)</f>
+        <v>-0.26136476413440751</v>
+      </c>
+      <c r="L58" s="9" t="str">
+        <f>TEXT(F58,"0.00") &amp; " (" &amp; TEXT(H58,"0.00") &amp; "–" &amp; TEXT(J58,"0.00") &amp; ")"</f>
+        <v>0.49 (0.31–0.77)</v>
+      </c>
+      <c r="M58" s="8">
+        <v>0.69399999999999995</v>
+      </c>
+      <c r="N58" s="1">
+        <v>4</v>
+      </c>
+      <c r="O58" s="1">
         <v>10</v>
       </c>
-      <c r="F58" s="3"/>
-      <c r="G58" s="8" t="e">
-        <f>LN(F58)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H58" s="3"/>
-      <c r="I58" s="8" t="e">
-        <f>LN(H58)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J58" s="3"/>
-      <c r="K58" s="8" t="e">
-        <f>LN(J58)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L58" s="8" t="str">
-        <f>TEXT(F58,"0.00") &amp; " (" &amp; TEXT(H58,"0.00") &amp; "–" &amp; TEXT(J58,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M58" s="9"/>
-      <c r="N58" s="1"/>
-      <c r="O58" s="1"/>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="B59" t="s">
         <v>26</v>
@@ -3172,72 +3856,553 @@
         <v>23</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E59" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F59" s="7">
+        <v>0.9</v>
+      </c>
+      <c r="G59" s="7">
+        <f t="shared" si="4"/>
+        <v>-0.10536051565782628</v>
+      </c>
+      <c r="H59" s="7">
+        <v>0.69</v>
+      </c>
+      <c r="I59" s="7">
+        <f t="shared" si="5"/>
+        <v>-0.37106368139083207</v>
+      </c>
+      <c r="J59" s="7">
+        <v>1.19</v>
+      </c>
+      <c r="K59" s="7">
+        <f t="shared" si="6"/>
+        <v>0.17395330712343798</v>
+      </c>
+      <c r="L59" s="7" t="str">
+        <f t="shared" si="7"/>
+        <v>0.90 (0.69–1.19)</v>
+      </c>
+      <c r="M59" s="8">
+        <v>0.252</v>
+      </c>
+      <c r="N59" s="1">
+        <v>6</v>
+      </c>
+      <c r="O59" s="1">
         <v>8</v>
       </c>
-      <c r="F59" s="3"/>
-      <c r="G59" s="8" t="e">
-        <f>LN(F59)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H59" s="3"/>
-      <c r="I59" s="8" t="e">
-        <f>LN(H59)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J59" s="3"/>
-      <c r="K59" s="8" t="e">
-        <f>LN(J59)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L59" s="8" t="str">
-        <f>TEXT(F59,"0.00") &amp; " (" &amp; TEXT(H59,"0.00") &amp; "–" &amp; TEXT(J59,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M59" s="9"/>
-      <c r="N59" s="1"/>
-      <c r="O59" s="1"/>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="B60" t="s">
         <v>26</v>
       </c>
       <c r="C60" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F60" s="3">
+        <v>1.26</v>
+      </c>
+      <c r="G60" s="7">
+        <f>LN(F60)</f>
+        <v>0.23111172096338664</v>
+      </c>
+      <c r="H60" s="3">
+        <v>0.67</v>
+      </c>
+      <c r="I60" s="7">
+        <f>LN(H60)</f>
+        <v>-0.40047756659712525</v>
+      </c>
+      <c r="J60" s="3">
+        <v>2.35</v>
+      </c>
+      <c r="K60" s="7">
+        <f>LN(J60)</f>
+        <v>0.85441532815606758</v>
+      </c>
+      <c r="L60" s="7" t="str">
+        <f>TEXT(F60,"0.00") &amp; " (" &amp; TEXT(H60,"0.00") &amp; "–" &amp; TEXT(J60,"0.00") &amp; ")"</f>
+        <v>1.26 (0.67–2.35)</v>
+      </c>
+      <c r="M60" s="8">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="N60" s="1">
+        <v>3</v>
+      </c>
+      <c r="O60" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>26</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F61" s="3">
+        <v>0.88</v>
+      </c>
+      <c r="G61" s="7">
+        <f>LN(F61)</f>
+        <v>-0.12783337150988489</v>
+      </c>
+      <c r="H61" s="3">
+        <v>0.67</v>
+      </c>
+      <c r="I61" s="7">
+        <f>LN(H61)</f>
+        <v>-0.40047756659712525</v>
+      </c>
+      <c r="J61" s="3">
+        <v>1.17</v>
+      </c>
+      <c r="K61" s="7">
+        <f>LN(J61)</f>
+        <v>0.15700374880966469</v>
+      </c>
+      <c r="L61" s="7" t="str">
+        <f>TEXT(F61,"0.00") &amp; " (" &amp; TEXT(H61,"0.00") &amp; "–" &amp; TEXT(J61,"0.00") &amp; ")"</f>
+        <v>0.88 (0.67–1.17)</v>
+      </c>
+      <c r="M61" s="8">
+        <v>0.124</v>
+      </c>
+      <c r="N61" s="1">
+        <v>6</v>
+      </c>
+      <c r="O61" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>26</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F62" s="3">
+        <v>1.18</v>
+      </c>
+      <c r="G62" s="7">
+        <f t="shared" si="4"/>
+        <v>0.16551443847757333</v>
+      </c>
+      <c r="H62" s="3">
+        <v>0.51</v>
+      </c>
+      <c r="I62" s="7">
+        <f t="shared" si="5"/>
+        <v>-0.67334455326376563</v>
+      </c>
+      <c r="J62" s="3">
+        <v>2.72</v>
+      </c>
+      <c r="K62" s="7">
+        <f t="shared" si="6"/>
+        <v>1.000631880307906</v>
+      </c>
+      <c r="L62" s="7" t="str">
+        <f t="shared" si="7"/>
+        <v>1.18 (0.51–2.72)</v>
+      </c>
+      <c r="M62" s="8">
+        <v>0.66900000000000004</v>
+      </c>
+      <c r="N62" s="1">
+        <v>4</v>
+      </c>
+      <c r="O62" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>26</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F63" s="3">
+        <v>1.57</v>
+      </c>
+      <c r="G63" s="7">
+        <f>LN(F63)</f>
+        <v>0.45107561936021673</v>
+      </c>
+      <c r="H63" s="3">
+        <v>0.67</v>
+      </c>
+      <c r="I63" s="7">
+        <f>LN(H63)</f>
+        <v>-0.40047756659712525</v>
+      </c>
+      <c r="J63" s="3">
+        <v>3.66</v>
+      </c>
+      <c r="K63" s="7">
+        <f>LN(J63)</f>
+        <v>1.297463147413275</v>
+      </c>
+      <c r="L63" s="7" t="str">
+        <f>TEXT(F63,"0.00") &amp; " (" &amp; TEXT(H63,"0.00") &amp; "–" &amp; TEXT(J63,"0.00") &amp; ")"</f>
+        <v>1.57 (0.67–3.66)</v>
+      </c>
+      <c r="M63" s="8">
+        <v>0.61499999999999999</v>
+      </c>
+      <c r="N63" s="1">
+        <v>3</v>
+      </c>
+      <c r="O63" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>26</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F64" s="3">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="G64" s="7">
+        <f>LN(F64)</f>
+        <v>0.13976194237515863</v>
+      </c>
+      <c r="H64" s="3">
+        <v>0.51</v>
+      </c>
+      <c r="I64" s="7">
+        <f>LN(H64)</f>
+        <v>-0.67334455326376563</v>
+      </c>
+      <c r="J64" s="3">
+        <v>2.58</v>
+      </c>
+      <c r="K64" s="7">
+        <f>LN(J64)</f>
+        <v>0.94778939893352609</v>
+      </c>
+      <c r="L64" s="7" t="str">
+        <f>TEXT(F64,"0.00") &amp; " (" &amp; TEXT(H64,"0.00") &amp; "–" &amp; TEXT(J64,"0.00") &amp; ")"</f>
+        <v>1.15 (0.51–2.58)</v>
+      </c>
+      <c r="M64" s="8">
+        <v>0.61299999999999999</v>
+      </c>
+      <c r="N64" s="1">
+        <v>4</v>
+      </c>
+      <c r="O64" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>26</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F65" s="7">
+        <v>0.67</v>
+      </c>
+      <c r="G65" s="7">
+        <f t="shared" si="4"/>
+        <v>-0.40047756659712525</v>
+      </c>
+      <c r="H65" s="7">
+        <v>0.51</v>
+      </c>
+      <c r="I65" s="7">
+        <f t="shared" si="5"/>
+        <v>-0.67334455326376563</v>
+      </c>
+      <c r="J65" s="7">
+        <v>0.88</v>
+      </c>
+      <c r="K65" s="7">
+        <f t="shared" si="6"/>
+        <v>-0.12783337150988489</v>
+      </c>
+      <c r="L65" s="7" t="str">
+        <f t="shared" si="7"/>
+        <v>0.67 (0.51–0.88)</v>
+      </c>
+      <c r="M65" s="8">
+        <v>0.114</v>
+      </c>
+      <c r="N65" s="1">
+        <v>4</v>
+      </c>
+      <c r="O65" s="9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>26</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F66" s="3">
+        <v>0.89</v>
+      </c>
+      <c r="G66" s="7">
+        <f t="shared" si="4"/>
+        <v>-0.11653381625595151</v>
+      </c>
+      <c r="H66" s="3">
+        <v>0.81</v>
+      </c>
+      <c r="I66" s="7">
+        <f t="shared" si="5"/>
+        <v>-0.21072103131565253</v>
+      </c>
+      <c r="J66" s="3">
+        <v>0.98</v>
+      </c>
+      <c r="K66" s="7">
+        <f t="shared" si="6"/>
+        <v>-2.0202707317519466E-2</v>
+      </c>
+      <c r="L66" s="7" t="str">
+        <f t="shared" si="7"/>
+        <v>0.89 (0.81–0.98)</v>
+      </c>
+      <c r="M66" s="8">
+        <v>0.372</v>
+      </c>
+      <c r="N66" s="1">
+        <v>3</v>
+      </c>
+      <c r="O66" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>26</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F67" s="3">
+        <v>0.88</v>
+      </c>
+      <c r="G67" s="7">
+        <f t="shared" si="4"/>
+        <v>-0.12783337150988489</v>
+      </c>
+      <c r="H67" s="3">
+        <v>0.79</v>
+      </c>
+      <c r="I67" s="7">
+        <f t="shared" si="5"/>
+        <v>-0.23572233352106983</v>
+      </c>
+      <c r="J67" s="3">
+        <v>0.98</v>
+      </c>
+      <c r="K67" s="7">
+        <f t="shared" si="6"/>
+        <v>-2.0202707317519466E-2</v>
+      </c>
+      <c r="L67" s="7" t="str">
+        <f t="shared" si="7"/>
+        <v>0.88 (0.79–0.98)</v>
+      </c>
+      <c r="M67" s="8">
+        <v>0.20300000000000001</v>
+      </c>
+      <c r="N67" s="1">
+        <v>5</v>
+      </c>
+      <c r="O67" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A68" s="1"/>
+      <c r="B68" t="s">
+        <v>26</v>
+      </c>
+      <c r="C68" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D60" s="3" t="s">
+      <c r="D68" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E60" s="3" t="s">
+      <c r="E68" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F68" s="3">
+        <v>0.67</v>
+      </c>
+      <c r="G68" s="7">
+        <f>LN(F68)</f>
+        <v>-0.40047756659712525</v>
+      </c>
+      <c r="H68" s="3">
+        <v>0.54</v>
+      </c>
+      <c r="I68" s="7">
+        <f>LN(H68)</f>
+        <v>-0.61618613942381695</v>
+      </c>
+      <c r="J68" s="3">
+        <v>0.84</v>
+      </c>
+      <c r="K68" s="7">
+        <f>LN(J68)</f>
+        <v>-0.1743533871447778</v>
+      </c>
+      <c r="L68" s="7" t="str">
+        <f>TEXT(F68,"0.00") &amp; " (" &amp; TEXT(H68,"0.00") &amp; "–" &amp; TEXT(J68,"0.00") &amp; ")"</f>
+        <v>0.67 (0.54–0.84)</v>
+      </c>
+      <c r="M68" s="8">
+        <v>0.114</v>
+      </c>
+      <c r="N68" s="1">
+        <v>4</v>
+      </c>
+      <c r="O68" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
+        <v>67</v>
+      </c>
+      <c r="B69" t="s">
+        <v>26</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E69" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F60" s="3"/>
-      <c r="G60" s="8" t="e">
-        <f>LN(F60)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="H60" s="3"/>
-      <c r="I60" s="8" t="e">
-        <f>LN(H60)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="J60" s="3"/>
-      <c r="K60" s="8" t="e">
-        <f>LN(J60)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L60" s="8" t="str">
-        <f>TEXT(F60,"0.00") &amp; " (" &amp; TEXT(H60,"0.00") &amp; "–" &amp; TEXT(J60,"0.00") &amp; ")"</f>
-        <v>0.00 (0.00–0.00)</v>
-      </c>
-      <c r="M60" s="9"/>
-      <c r="N60" s="1"/>
-      <c r="O60" s="1"/>
+      <c r="F69" s="3">
+        <v>0.72</v>
+      </c>
+      <c r="G69" s="7">
+        <f t="shared" si="4"/>
+        <v>-0.3285040669720361</v>
+      </c>
+      <c r="H69" s="3">
+        <v>0.49</v>
+      </c>
+      <c r="I69" s="7">
+        <f t="shared" si="5"/>
+        <v>-0.71334988787746478</v>
+      </c>
+      <c r="J69" s="3">
+        <v>1.06</v>
+      </c>
+      <c r="K69" s="7">
+        <f t="shared" si="6"/>
+        <v>5.8268908123975824E-2</v>
+      </c>
+      <c r="L69" s="7" t="str">
+        <f t="shared" si="7"/>
+        <v>0.72 (0.49–1.06)</v>
+      </c>
+      <c r="M69" s="8">
+        <v>0.46100000000000002</v>
+      </c>
+      <c r="N69" s="1">
+        <v>3</v>
+      </c>
+      <c r="O69" s="1">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
